--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA266"/>
+  <dimension ref="A1:AA269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -30628,6 +30628,317 @@
       <c r="Z266" s="2" t="inlineStr"/>
       <c r="AA266" s="2" t="inlineStr"/>
     </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Vinos Limited</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Vinos Limited</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 12</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Western Parkway Business Park, Unit 77 Ballymount Road Lower, Robinhood</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>D12 XW99</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>https://bacchus.ie</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>henryanderson@bacchus.ie</t>
+        </is>
+      </c>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 450 5046</t>
+        </is>
+      </c>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>473415</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="inlineStr"/>
+      <c r="S267" s="2" t="inlineStr"/>
+      <c r="T267" s="2" t="inlineStr"/>
+      <c r="U267" s="2" t="inlineStr"/>
+      <c r="V267" s="2" t="inlineStr"/>
+      <c r="W267" s="2" t="inlineStr">
+        <is>
+          <t>Michael Doyle</t>
+        </is>
+      </c>
+      <c r="X267" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y267" s="2" t="inlineStr"/>
+      <c r="Z267" s="2" t="inlineStr"/>
+      <c r="AA267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-doyle-253aa689/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Vinos Limited</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Vinos Limited</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 12</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Western Parkway Business Park, Unit 77 Ballymount Road Lower, Robinhood</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>D12 XW99</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>https://bacchus.ie</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t>henryanderson@bacchus.ie</t>
+        </is>
+      </c>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 450 5046</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>473415</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="inlineStr"/>
+      <c r="S268" s="2" t="inlineStr"/>
+      <c r="T268" s="2" t="inlineStr"/>
+      <c r="U268" s="2" t="inlineStr"/>
+      <c r="V268" s="2" t="inlineStr"/>
+      <c r="W268" s="2" t="inlineStr">
+        <is>
+          <t>Henry Anderson</t>
+        </is>
+      </c>
+      <c r="X268" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y268" s="2" t="inlineStr"/>
+      <c r="Z268" s="2" t="inlineStr"/>
+      <c r="AA268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/henry-anderson-505b0959/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Sheridans Cheesemongers Ltd.</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Sheridans Cheesemongers Ltd.</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>46122</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Pottlereagh</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Co. Meath</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>Old Virginia Road</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>A82 K400</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>https://sheridanscheesemongers.com</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N269" s="2" t="inlineStr">
+        <is>
+          <t>kevin@sheridanscheesemongers.com</t>
+        </is>
+      </c>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>+353 46 924 5110</t>
+        </is>
+      </c>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q269" s="2" t="inlineStr"/>
+      <c r="R269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sheridans-cheesemongers-ltd-/</t>
+        </is>
+      </c>
+      <c r="S269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SheridansCheese</t>
+        </is>
+      </c>
+      <c r="T269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sheridanscheese</t>
+        </is>
+      </c>
+      <c r="U269" s="2" t="inlineStr"/>
+      <c r="V269" s="2" t="inlineStr"/>
+      <c r="W269" s="2" t="inlineStr">
+        <is>
+          <t>Kevin Sheridan</t>
+        </is>
+      </c>
+      <c r="X269" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y269" s="2" t="inlineStr"/>
+      <c r="Z269" s="2" t="inlineStr"/>
+      <c r="AA269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kevin-sheridan-aa1b6bb3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA269"/>
+  <dimension ref="A1:AA276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -30939,6 +30939,785 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Molloy Holdings Limited</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Molloy Holdings Limited</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>60183</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>2 Village Green, Tallaght</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>D24 X335</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>https://molloys.ie, https://molloysexpress.ie</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>info@molloys.ie</t>
+        </is>
+      </c>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 451 5544</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>58254</t>
+        </is>
+      </c>
+      <c r="R270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/molloy-group</t>
+        </is>
+      </c>
+      <c r="S270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/molloysliquor/</t>
+        </is>
+      </c>
+      <c r="T270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/molloysliquorstores</t>
+        </is>
+      </c>
+      <c r="U270" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/molloysliquor</t>
+        </is>
+      </c>
+      <c r="V270" s="2" t="inlineStr"/>
+      <c r="W270" s="2" t="inlineStr">
+        <is>
+          <t>Richard Molloy</t>
+        </is>
+      </c>
+      <c r="X270" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y270" s="2" t="inlineStr"/>
+      <c r="Z270" s="2" t="inlineStr"/>
+      <c r="AA270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-molloy-100352134/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Molloy Holdings Limited</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Molloy Holdings Limited</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>60183</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>2 Village Green, Tallaght</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>D24 X335</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>https://molloys.ie, https://molloysexpress.ie</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>info@molloys.ie</t>
+        </is>
+      </c>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 451 5544</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>58254</t>
+        </is>
+      </c>
+      <c r="R271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/molloy-group</t>
+        </is>
+      </c>
+      <c r="S271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/molloysliquor/</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/molloysliquorstores</t>
+        </is>
+      </c>
+      <c r="U271" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/molloysliquor</t>
+        </is>
+      </c>
+      <c r="V271" s="2" t="inlineStr"/>
+      <c r="W271" s="2" t="inlineStr">
+        <is>
+          <t>Mick Burke</t>
+        </is>
+      </c>
+      <c r="X271" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y271" s="2" t="inlineStr"/>
+      <c r="Z271" s="2" t="inlineStr"/>
+      <c r="AA271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mick-burke-57a2abb9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Molloy Holdings Limited</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>Molloy Holdings Limited</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>60183</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>2 Village Green, Tallaght</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>D24 X335</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>https://molloys.ie, https://molloysexpress.ie</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N272" s="2" t="inlineStr">
+        <is>
+          <t>info@molloys.ie</t>
+        </is>
+      </c>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 451 5544</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>58254</t>
+        </is>
+      </c>
+      <c r="R272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/molloy-group</t>
+        </is>
+      </c>
+      <c r="S272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/molloysliquor/</t>
+        </is>
+      </c>
+      <c r="T272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/molloysliquorstores</t>
+        </is>
+      </c>
+      <c r="U272" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/molloysliquor</t>
+        </is>
+      </c>
+      <c r="V272" s="2" t="inlineStr"/>
+      <c r="W272" s="2" t="inlineStr">
+        <is>
+          <t>Shane O'Regan</t>
+        </is>
+      </c>
+      <c r="X272" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y272" s="2" t="inlineStr"/>
+      <c r="Z272" s="2" t="inlineStr"/>
+      <c r="AA272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shane-o-regan-b29b1b176/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>The Wicklow Wine Company</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>The Wicklow Wine Company</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>8012</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Wicklow</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>7 Main Street, Corporation Lands</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>A67 VN23</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>https://wicklowwineco.ie</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t>shop@wicklowwineco.ie</t>
+        </is>
+      </c>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>+353 404 66767</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>330546</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-wicklow-wine-company/</t>
+        </is>
+      </c>
+      <c r="S273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WicklowWine/</t>
+        </is>
+      </c>
+      <c r="T273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thewicklowwineco/?hl=en</t>
+        </is>
+      </c>
+      <c r="U273" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/wicklowwine</t>
+        </is>
+      </c>
+      <c r="V273" s="2" t="inlineStr"/>
+      <c r="W273" s="2" t="inlineStr">
+        <is>
+          <t>David Dunne</t>
+        </is>
+      </c>
+      <c r="X273" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y273" s="2" t="inlineStr"/>
+      <c r="Z273" s="2" t="inlineStr"/>
+      <c r="AA273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-dunne-51566322b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Vinos Limited</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Vinos Limited</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 12</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>Western Parkway Business Park, Unit 77 Ballymount Road Lower, Robinhood</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>D12 XW99</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>https://bacchus.ie</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>henryanderson@bacchus.ie</t>
+        </is>
+      </c>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 450 5046</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>473415</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="inlineStr"/>
+      <c r="S274" s="2" t="inlineStr"/>
+      <c r="T274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="inlineStr"/>
+      <c r="V274" s="2" t="inlineStr"/>
+      <c r="W274" s="2" t="inlineStr">
+        <is>
+          <t>Henry Anderson</t>
+        </is>
+      </c>
+      <c r="X274" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y274" s="2" t="inlineStr"/>
+      <c r="Z274" s="2" t="inlineStr"/>
+      <c r="AA274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/henry-anderson-505b0959/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Vinos Limited</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Vinos Limited</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 12</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>Western Parkway Business Park, Unit 77 Ballymount Road Lower, Robinhood</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>D12 XW99</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>https://bacchus.ie</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr"/>
+      <c r="K275" s="2" t="inlineStr"/>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N275" s="2" t="inlineStr">
+        <is>
+          <t>henryanderson@bacchus.ie</t>
+        </is>
+      </c>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 450 5046</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>473415</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="inlineStr"/>
+      <c r="S275" s="2" t="inlineStr"/>
+      <c r="T275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="inlineStr"/>
+      <c r="V275" s="2" t="inlineStr"/>
+      <c r="W275" s="2" t="inlineStr">
+        <is>
+          <t>Michael Doyle</t>
+        </is>
+      </c>
+      <c r="X275" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y275" s="2" t="inlineStr"/>
+      <c r="Z275" s="2" t="inlineStr"/>
+      <c r="AA275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-doyle-253aa689/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Sheridans Cheesemongers Ltd.</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Sheridans Cheesemongers Ltd.</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>46122</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Pottlereagh</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Co. Meath</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>Old Virginia Road</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>A82 K400</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>https://sheridanscheesemongers.com</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr"/>
+      <c r="K276" s="2" t="inlineStr"/>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N276" s="2" t="inlineStr">
+        <is>
+          <t>kevin@sheridanscheesemongers.com</t>
+        </is>
+      </c>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>+353 46 924 5110</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q276" s="2" t="inlineStr"/>
+      <c r="R276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sheridans-cheesemongers-ltd-/</t>
+        </is>
+      </c>
+      <c r="S276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SheridansCheese</t>
+        </is>
+      </c>
+      <c r="T276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sheridanscheese</t>
+        </is>
+      </c>
+      <c r="U276" s="2" t="inlineStr"/>
+      <c r="V276" s="2" t="inlineStr"/>
+      <c r="W276" s="2" t="inlineStr">
+        <is>
+          <t>Kevin Sheridan</t>
+        </is>
+      </c>
+      <c r="X276" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y276" s="2" t="inlineStr"/>
+      <c r="Z276" s="2" t="inlineStr"/>
+      <c r="AA276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kevin-sheridan-aa1b6bb3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA276"/>
+  <dimension ref="A1:AA285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -31718,6 +31718,895 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>WINE WEB LIMITED</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr"/>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>167813</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Swords</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>Unit 2 Snows Yard</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr"/>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>https://wineweb.ie</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr"/>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr"/>
+      <c r="M277" s="2" t="inlineStr">
+        <is>
+          <t>77990</t>
+        </is>
+      </c>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>sales@wineweb.ie</t>
+        </is>
+      </c>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 861 2951</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>392764</t>
+        </is>
+      </c>
+      <c r="R277" s="2" t="inlineStr"/>
+      <c r="S277" s="2" t="inlineStr"/>
+      <c r="T277" s="2" t="inlineStr"/>
+      <c r="U277" s="2" t="inlineStr"/>
+      <c r="V277" s="2" t="inlineStr"/>
+      <c r="W277" s="2" t="inlineStr">
+        <is>
+          <t>Liam Meaney</t>
+        </is>
+      </c>
+      <c r="X277" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y277" s="2" t="inlineStr"/>
+      <c r="Z277" s="2" t="inlineStr"/>
+      <c r="AA277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/liam-meaney-20325b1b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>WINE WEB LIMITED</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr"/>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>167813</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Swords</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr"/>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>Unit 2 Snows Yard</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr"/>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>https://wineweb.ie</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr"/>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
+          <t>77990</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>sales@wineweb.ie</t>
+        </is>
+      </c>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 861 2951</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>392764</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="inlineStr"/>
+      <c r="S278" s="2" t="inlineStr"/>
+      <c r="T278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="inlineStr"/>
+      <c r="V278" s="2" t="inlineStr"/>
+      <c r="W278" s="2" t="inlineStr">
+        <is>
+          <t>Julie Flanagan</t>
+        </is>
+      </c>
+      <c r="X278" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y278" s="2" t="inlineStr"/>
+      <c r="Z278" s="2" t="inlineStr"/>
+      <c r="AA278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>TASTE OF GEORGIA LIMITED</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr"/>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>167806</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr"/>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>Coolmine Industrial Estate</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>D15 X981</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>https://tasteofgeorgiaire.com</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr"/>
+      <c r="K279" s="2" t="inlineStr"/>
+      <c r="L279" s="2" t="inlineStr"/>
+      <c r="M279" s="2" t="inlineStr">
+        <is>
+          <t>43511</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>tasteofgeorgiaire@gmail.com</t>
+        </is>
+      </c>
+      <c r="O279" s="2" t="inlineStr"/>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>701993</t>
+        </is>
+      </c>
+      <c r="R279" s="2" t="inlineStr"/>
+      <c r="S279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100089306260958</t>
+        </is>
+      </c>
+      <c r="T279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tasteofgeorgiaire/</t>
+        </is>
+      </c>
+      <c r="U279" s="2" t="inlineStr"/>
+      <c r="V279" s="2" t="inlineStr"/>
+      <c r="W279" s="2" t="inlineStr">
+        <is>
+          <t>Vakhtang Abdaladze</t>
+        </is>
+      </c>
+      <c r="X279" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y279" s="2" t="inlineStr"/>
+      <c r="Z279" s="2" t="inlineStr"/>
+      <c r="AA279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vakhtang-abdaladze-874967a6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>TASTE OF GEORGIA LIMITED</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr"/>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>167806</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr"/>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>Coolmine Industrial Estate</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>D15 X981</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>https://tasteofgeorgiaire.com</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr"/>
+      <c r="K280" s="2" t="inlineStr"/>
+      <c r="L280" s="2" t="inlineStr"/>
+      <c r="M280" s="2" t="inlineStr">
+        <is>
+          <t>43511</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>tasteofgeorgiaire@gmail.com</t>
+        </is>
+      </c>
+      <c r="O280" s="2" t="inlineStr"/>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>701993</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr"/>
+      <c r="S280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100089306260958</t>
+        </is>
+      </c>
+      <c r="T280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tasteofgeorgiaire/</t>
+        </is>
+      </c>
+      <c r="U280" s="2" t="inlineStr"/>
+      <c r="V280" s="2" t="inlineStr"/>
+      <c r="W280" s="2" t="inlineStr">
+        <is>
+          <t>Guguli Abdaladze</t>
+        </is>
+      </c>
+      <c r="X280" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y280" s="2" t="inlineStr"/>
+      <c r="Z280" s="2" t="inlineStr"/>
+      <c r="AA280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>TASTE OF GEORGIA LIMITED</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr"/>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>167806</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr"/>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>Coolmine Industrial Estate</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>D15 X981</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>https://tasteofgeorgiaire.com</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr"/>
+      <c r="K281" s="2" t="inlineStr"/>
+      <c r="L281" s="2" t="inlineStr"/>
+      <c r="M281" s="2" t="inlineStr">
+        <is>
+          <t>43511</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>tasteofgeorgiaire@gmail.com</t>
+        </is>
+      </c>
+      <c r="O281" s="2" t="inlineStr"/>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>701993</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="inlineStr"/>
+      <c r="S281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100089306260958</t>
+        </is>
+      </c>
+      <c r="T281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tasteofgeorgiaire/</t>
+        </is>
+      </c>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" s="2" t="inlineStr"/>
+      <c r="W281" s="2" t="inlineStr">
+        <is>
+          <t>Luca Abdaladze</t>
+        </is>
+      </c>
+      <c r="X281" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y281" s="2" t="inlineStr"/>
+      <c r="Z281" s="2" t="inlineStr"/>
+      <c r="AA281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Wines Direct Limited</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Wines Direct Limited</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>Mullingar</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>County Westmeath</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>49 Lough Sheever Corporate Park</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>N91 V658</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>https://winesdirect.ie</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="2" t="inlineStr"/>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr"/>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>online@winesdirect.ie</t>
+        </is>
+      </c>
+      <c r="O282" s="2" t="inlineStr">
+        <is>
+          <t>+353 818 579 579</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>180434</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wines-direct-ltd</t>
+        </is>
+      </c>
+      <c r="S282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winesdirect/</t>
+        </is>
+      </c>
+      <c r="T282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winesdirectirl</t>
+        </is>
+      </c>
+      <c r="U282" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winesdirect</t>
+        </is>
+      </c>
+      <c r="V282" s="2" t="inlineStr"/>
+      <c r="W282" s="2" t="inlineStr">
+        <is>
+          <t>Gareth Keogh</t>
+        </is>
+      </c>
+      <c r="X282" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y282" s="2" t="inlineStr"/>
+      <c r="Z282" s="2" t="inlineStr"/>
+      <c r="AA282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gareth-keogh-b5a67a66/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Wines Direct Limited</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Wines Direct Limited</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>Mullingar</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>County Westmeath</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>49 Lough Sheever Corporate Park</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>N91 V658</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>https://winesdirect.ie</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr"/>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr"/>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>online@winesdirect.ie</t>
+        </is>
+      </c>
+      <c r="O283" s="2" t="inlineStr">
+        <is>
+          <t>+353 818 579 579</t>
+        </is>
+      </c>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>180434</t>
+        </is>
+      </c>
+      <c r="R283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wines-direct-ltd</t>
+        </is>
+      </c>
+      <c r="S283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winesdirect/</t>
+        </is>
+      </c>
+      <c r="T283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winesdirectirl</t>
+        </is>
+      </c>
+      <c r="U283" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winesdirect</t>
+        </is>
+      </c>
+      <c r="V283" s="2" t="inlineStr"/>
+      <c r="W283" s="2" t="inlineStr">
+        <is>
+          <t>Fiona Kealy</t>
+        </is>
+      </c>
+      <c r="X283" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing &amp; Inventory Manager</t>
+        </is>
+      </c>
+      <c r="Y283" s="2" t="inlineStr"/>
+      <c r="Z283" s="2" t="inlineStr"/>
+      <c r="AA283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fiona-kealy-62250517/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Wines Direct Limited</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Wines Direct Limited</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Mullingar</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>County Westmeath</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>49 Lough Sheever Corporate Park</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>N91 V658</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>https://winesdirect.ie</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="inlineStr"/>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>online@winesdirect.ie</t>
+        </is>
+      </c>
+      <c r="O284" s="2" t="inlineStr">
+        <is>
+          <t>+353 818 579 579</t>
+        </is>
+      </c>
+      <c r="P284" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>180434</t>
+        </is>
+      </c>
+      <c r="R284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wines-direct-ltd</t>
+        </is>
+      </c>
+      <c r="S284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winesdirect/</t>
+        </is>
+      </c>
+      <c r="T284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winesdirectirl</t>
+        </is>
+      </c>
+      <c r="U284" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winesdirect</t>
+        </is>
+      </c>
+      <c r="V284" s="2" t="inlineStr"/>
+      <c r="W284" s="2" t="inlineStr">
+        <is>
+          <t>Guillaume LaSalle</t>
+        </is>
+      </c>
+      <c r="X284" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y284" s="2" t="inlineStr"/>
+      <c r="Z284" s="2" t="inlineStr"/>
+      <c r="AA284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/guillaume-lasalle-a77b6235/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Wines Direct Limited</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Wines Direct Limited</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>Mullingar</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>County Westmeath</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>49 Lough Sheever Corporate Park</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>N91 V658</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>https://winesdirect.ie</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr"/>
+      <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr"/>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>online@winesdirect.ie</t>
+        </is>
+      </c>
+      <c r="O285" s="2" t="inlineStr">
+        <is>
+          <t>+353 818 579 579</t>
+        </is>
+      </c>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>180434</t>
+        </is>
+      </c>
+      <c r="R285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wines-direct-ltd</t>
+        </is>
+      </c>
+      <c r="S285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winesdirect/</t>
+        </is>
+      </c>
+      <c r="T285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winesdirectirl</t>
+        </is>
+      </c>
+      <c r="U285" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winesdirect</t>
+        </is>
+      </c>
+      <c r="V285" s="2" t="inlineStr"/>
+      <c r="W285" s="2" t="inlineStr">
+        <is>
+          <t>Gavin Keogh</t>
+        </is>
+      </c>
+      <c r="X285" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y285" s="2" t="inlineStr"/>
+      <c r="Z285" s="2" t="inlineStr"/>
+      <c r="AA285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gavinkeogh/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA285"/>
+  <dimension ref="A1:AA289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -32607,6 +32607,374 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Edward Dillon &amp; Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Edward Dillon &amp; Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>7972</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 3</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>Estuary House, Block P7, East Point Business Park, Fairview</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>D03 AV27</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edwarddillonco.ie</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="inlineStr"/>
+      <c r="L286" s="2" t="inlineStr"/>
+      <c r="M286" s="2" t="inlineStr"/>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>salesoffice@edwarddillonco.ie</t>
+        </is>
+      </c>
+      <c r="O286" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 819 3300</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="inlineStr"/>
+      <c r="Q286" s="2" t="inlineStr"/>
+      <c r="R286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/edward-dillon-&amp;-co.-ltd</t>
+        </is>
+      </c>
+      <c r="S286" s="2" t="inlineStr"/>
+      <c r="T286" s="2" t="inlineStr"/>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" s="2" t="inlineStr"/>
+      <c r="W286" s="2" t="inlineStr">
+        <is>
+          <t>Eamonn Brew</t>
+        </is>
+      </c>
+      <c r="X286" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Executive</t>
+        </is>
+      </c>
+      <c r="Y286" s="2" t="inlineStr"/>
+      <c r="Z286" s="2" t="inlineStr"/>
+      <c r="AA286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eamonn-brew-b7a051201/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Edward Dillon &amp; Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>Edward Dillon &amp; Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>7972</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 3</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>Estuary House, Block P7, East Point Business Park, Fairview</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>D03 AV27</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edwarddillonco.ie</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr"/>
+      <c r="K287" s="2" t="inlineStr"/>
+      <c r="L287" s="2" t="inlineStr"/>
+      <c r="M287" s="2" t="inlineStr"/>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>salesoffice@edwarddillonco.ie</t>
+        </is>
+      </c>
+      <c r="O287" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 819 3300</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="inlineStr"/>
+      <c r="Q287" s="2" t="inlineStr"/>
+      <c r="R287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/edward-dillon-&amp;-co.-ltd</t>
+        </is>
+      </c>
+      <c r="S287" s="2" t="inlineStr"/>
+      <c r="T287" s="2" t="inlineStr"/>
+      <c r="U287" s="2" t="inlineStr"/>
+      <c r="V287" s="2" t="inlineStr"/>
+      <c r="W287" s="2" t="inlineStr">
+        <is>
+          <t>John Cassidy</t>
+        </is>
+      </c>
+      <c r="X287" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y287" s="2" t="inlineStr"/>
+      <c r="Z287" s="2" t="inlineStr"/>
+      <c r="AA287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-cassidy-7aabab17/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Newgate Wines Limited</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Newgate Wines Limited</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>8022</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>Drogheda</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>Co. Louth</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>Townrath Road, Ballymakenny</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>A92 A990</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>https://newgatewines.com</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr"/>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>niall.dunne@newgatewines.com</t>
+        </is>
+      </c>
+      <c r="O288" s="2" t="inlineStr">
+        <is>
+          <t>+353 41 984 3532</t>
+        </is>
+      </c>
+      <c r="P288" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
+          <t>353963</t>
+        </is>
+      </c>
+      <c r="R288" s="2" t="inlineStr"/>
+      <c r="S288" s="2" t="inlineStr"/>
+      <c r="T288" s="2" t="inlineStr"/>
+      <c r="U288" s="2" t="inlineStr"/>
+      <c r="V288" s="2" t="inlineStr"/>
+      <c r="W288" s="2" t="inlineStr">
+        <is>
+          <t>Niall Dunne</t>
+        </is>
+      </c>
+      <c r="X288" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y288" s="2" t="inlineStr"/>
+      <c r="Z288" s="2" t="inlineStr"/>
+      <c r="AA288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/niall-dunne-58603418/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Newgate Wines Limited</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>Newgate Wines Limited</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>8022</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>Drogheda</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>Co. Louth</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>Townrath Road, Ballymakenny</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>A92 A990</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>https://newgatewines.com</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr"/>
+      <c r="K289" s="2" t="inlineStr"/>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr"/>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>niall.dunne@newgatewines.com</t>
+        </is>
+      </c>
+      <c r="O289" s="2" t="inlineStr">
+        <is>
+          <t>+353 41 984 3532</t>
+        </is>
+      </c>
+      <c r="P289" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>353963</t>
+        </is>
+      </c>
+      <c r="R289" s="2" t="inlineStr"/>
+      <c r="S289" s="2" t="inlineStr"/>
+      <c r="T289" s="2" t="inlineStr"/>
+      <c r="U289" s="2" t="inlineStr"/>
+      <c r="V289" s="2" t="inlineStr"/>
+      <c r="W289" s="2" t="inlineStr">
+        <is>
+          <t>Michelle Dunne</t>
+        </is>
+      </c>
+      <c r="X289" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y289" s="2" t="inlineStr"/>
+      <c r="Z289" s="2" t="inlineStr"/>
+      <c r="AA289" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA289"/>
+  <dimension ref="A1:AA306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -32975,6 +32975,1847 @@
       <c r="Z289" s="2" t="inlineStr"/>
       <c r="AA289" s="2" t="inlineStr"/>
     </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Martins Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Martins Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>8038</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 3</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>11 Marino Mart, Marino</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>D03 K2R7</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>https://martinsofflicence.ie</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr"/>
+      <c r="K290" s="2" t="inlineStr"/>
+      <c r="L290" s="2" t="inlineStr"/>
+      <c r="M290" s="2" t="inlineStr"/>
+      <c r="N290" s="2" t="inlineStr">
+        <is>
+          <t>info@martinsofflicence.ie</t>
+        </is>
+      </c>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 833 2952</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>619182</t>
+        </is>
+      </c>
+      <c r="R290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/martins-off-licence/</t>
+        </is>
+      </c>
+      <c r="S290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/martins.offlicence</t>
+        </is>
+      </c>
+      <c r="T290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/martinsofflicence</t>
+        </is>
+      </c>
+      <c r="U290" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/martinsfairview</t>
+        </is>
+      </c>
+      <c r="V290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC1d1bEcsxSgMcnqzopNsALg</t>
+        </is>
+      </c>
+      <c r="W290" s="2" t="inlineStr">
+        <is>
+          <t>Damian Martin</t>
+        </is>
+      </c>
+      <c r="X290" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Manager</t>
+        </is>
+      </c>
+      <c r="Y290" s="2" t="inlineStr"/>
+      <c r="Z290" s="2" t="inlineStr"/>
+      <c r="AA290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/damian-martin-91964430/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Martins Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>Martins Off Licence Limited</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>8038</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 3</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>11 Marino Mart, Marino</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>D03 K2R7</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>https://martinsofflicence.ie</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr"/>
+      <c r="K291" s="2" t="inlineStr"/>
+      <c r="L291" s="2" t="inlineStr"/>
+      <c r="M291" s="2" t="inlineStr"/>
+      <c r="N291" s="2" t="inlineStr">
+        <is>
+          <t>info@martinsofflicence.ie</t>
+        </is>
+      </c>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 833 2952</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>619182</t>
+        </is>
+      </c>
+      <c r="R291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/martins-off-licence/</t>
+        </is>
+      </c>
+      <c r="S291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/martins.offlicence</t>
+        </is>
+      </c>
+      <c r="T291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/martinsofflicence</t>
+        </is>
+      </c>
+      <c r="U291" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/martinsfairview</t>
+        </is>
+      </c>
+      <c r="V291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC1d1bEcsxSgMcnqzopNsALg</t>
+        </is>
+      </c>
+      <c r="W291" s="2" t="inlineStr">
+        <is>
+          <t>Enda Molloy</t>
+        </is>
+      </c>
+      <c r="X291" s="2" t="inlineStr">
+        <is>
+          <t>Retail Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y291" s="2" t="inlineStr"/>
+      <c r="Z291" s="2" t="inlineStr"/>
+      <c r="AA291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/enda-molloy-068059125/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Greenacres (wexford) Ltd</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>Greenacres (wexford) Ltd</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>8036</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>Wexford</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>County Wexford</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>2 Selskar Street, Townparks</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>Y35 RW7C</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>https://greenacres.ie</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr"/>
+      <c r="K292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr"/>
+      <c r="N292" s="2" t="inlineStr">
+        <is>
+          <t>info@greenacres.ie</t>
+        </is>
+      </c>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>+353 53 912 2975</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>89721</t>
+        </is>
+      </c>
+      <c r="R292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/greenacres-wexford</t>
+        </is>
+      </c>
+      <c r="S292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/greenacreswexford/</t>
+        </is>
+      </c>
+      <c r="T292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/greenacresirl</t>
+        </is>
+      </c>
+      <c r="U292" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/greenacresirl</t>
+        </is>
+      </c>
+      <c r="V292" s="2" t="inlineStr"/>
+      <c r="W292" s="2" t="inlineStr">
+        <is>
+          <t>James G.</t>
+        </is>
+      </c>
+      <c r="X292" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y292" s="2" t="inlineStr"/>
+      <c r="Z292" s="2" t="inlineStr"/>
+      <c r="AA292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-g-o-connor-5373b169</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Greenacres (wexford) Ltd</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>Greenacres (wexford) Ltd</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>8036</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>Wexford</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>County Wexford</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>2 Selskar Street, Townparks</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>Y35 RW7C</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>https://greenacres.ie</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr"/>
+      <c r="K293" s="2" t="inlineStr"/>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr"/>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>info@greenacres.ie</t>
+        </is>
+      </c>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>+353 53 912 2975</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>89721</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/greenacres-wexford</t>
+        </is>
+      </c>
+      <c r="S293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/greenacreswexford/</t>
+        </is>
+      </c>
+      <c r="T293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/greenacresirl</t>
+        </is>
+      </c>
+      <c r="U293" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/greenacresirl</t>
+        </is>
+      </c>
+      <c r="V293" s="2" t="inlineStr"/>
+      <c r="W293" s="2" t="inlineStr">
+        <is>
+          <t>Donal Morris</t>
+        </is>
+      </c>
+      <c r="X293" s="2" t="inlineStr">
+        <is>
+          <t>Wine Merchant</t>
+        </is>
+      </c>
+      <c r="Y293" s="2" t="inlineStr"/>
+      <c r="Z293" s="2" t="inlineStr"/>
+      <c r="AA293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/donal-morris-98593848/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>The Vintry</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>The Vintry</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>8011</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 24</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>102 Rathgar Road D6</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>D24 CF96</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vintry.ie</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr"/>
+      <c r="K294" s="2" t="inlineStr"/>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr"/>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>vintry@vintry.ie</t>
+        </is>
+      </c>
+      <c r="O294" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 490 5477</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q294" s="2" t="inlineStr"/>
+      <c r="R294" s="2" t="inlineStr"/>
+      <c r="S294" s="2" t="inlineStr"/>
+      <c r="T294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thevintryrathgar/</t>
+        </is>
+      </c>
+      <c r="U294" s="2" t="inlineStr"/>
+      <c r="V294" s="2" t="inlineStr"/>
+      <c r="W294" s="2" t="inlineStr">
+        <is>
+          <t>Evelyn Jones</t>
+        </is>
+      </c>
+      <c r="X294" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y294" s="2" t="inlineStr"/>
+      <c r="Z294" s="2" t="inlineStr"/>
+      <c r="AA294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vintry-the-evelyn-jones-79973423/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>Next Door Trading Limited</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>Next Door Trading Limited</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>8028</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 14</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>Block D, Unit 16, Nutgrove Office Park, Rathfarnham</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>D14 EE38</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nextdoor.ie</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr"/>
+      <c r="K295" s="2" t="inlineStr"/>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr"/>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@nextdoor.ie</t>
+        </is>
+      </c>
+      <c r="O295" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 296 9111</t>
+        </is>
+      </c>
+      <c r="P295" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>275586</t>
+        </is>
+      </c>
+      <c r="R295" s="2" t="inlineStr"/>
+      <c r="S295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/nextdoorgroup</t>
+        </is>
+      </c>
+      <c r="T295" s="2" t="inlineStr"/>
+      <c r="U295" s="2" t="inlineStr"/>
+      <c r="V295" s="2" t="inlineStr"/>
+      <c r="W295" s="2" t="inlineStr">
+        <is>
+          <t>Brian O'Sullivan</t>
+        </is>
+      </c>
+      <c r="X295" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y295" s="2" t="inlineStr"/>
+      <c r="Z295" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brian-osullivan-retail-is-detail/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>Next Door Trading Limited</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>Next Door Trading Limited</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>8028</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 14</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>Block D, Unit 16, Nutgrove Office Park, Rathfarnham</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>D14 EE38</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nextdoor.ie</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr"/>
+      <c r="K296" s="2" t="inlineStr"/>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr"/>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@nextdoor.ie</t>
+        </is>
+      </c>
+      <c r="O296" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 296 9111</t>
+        </is>
+      </c>
+      <c r="P296" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>275586</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="inlineStr"/>
+      <c r="S296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/nextdoorgroup</t>
+        </is>
+      </c>
+      <c r="T296" s="2" t="inlineStr"/>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" s="2" t="inlineStr"/>
+      <c r="W296" s="2" t="inlineStr">
+        <is>
+          <t>Kevin Long</t>
+        </is>
+      </c>
+      <c r="X296" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y296" s="2" t="inlineStr"/>
+      <c r="Z296" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>Fallon &amp; Byrne Limited</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>Fallon &amp; Byrne Limited</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>8034</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>11-17 Exchequer Street</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>D02 RY63</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fallonandbyrne.com</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr"/>
+      <c r="K297" s="2" t="inlineStr"/>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr"/>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>wine@fallonandbyrne.com</t>
+        </is>
+      </c>
+      <c r="O297" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 472 1010</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>393383</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fallon-&amp;-byrne/</t>
+        </is>
+      </c>
+      <c r="S297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/FallonandByrne/</t>
+        </is>
+      </c>
+      <c r="T297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/FallonandByrne/</t>
+        </is>
+      </c>
+      <c r="U297" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/fallonandbyrne</t>
+        </is>
+      </c>
+      <c r="V297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@fallonbyrne9920/</t>
+        </is>
+      </c>
+      <c r="W297" s="2" t="inlineStr">
+        <is>
+          <t>Borislav Jovanov</t>
+        </is>
+      </c>
+      <c r="X297" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Buyer</t>
+        </is>
+      </c>
+      <c r="Y297" s="2" t="inlineStr"/>
+      <c r="Z297" s="2" t="inlineStr"/>
+      <c r="AA297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/borislav-jovanov-18b978ba/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>Fallon &amp; Byrne Limited</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>Fallon &amp; Byrne Limited</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>8034</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>11-17 Exchequer Street</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>D02 RY63</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fallonandbyrne.com</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr"/>
+      <c r="K298" s="2" t="inlineStr"/>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr"/>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>wine@fallonandbyrne.com</t>
+        </is>
+      </c>
+      <c r="O298" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 472 1010</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>393383</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fallon-&amp;-byrne/</t>
+        </is>
+      </c>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/FallonandByrne/</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/FallonandByrne/</t>
+        </is>
+      </c>
+      <c r="U298" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/fallonandbyrne</t>
+        </is>
+      </c>
+      <c r="V298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@fallonbyrne9920/</t>
+        </is>
+      </c>
+      <c r="W298" s="2" t="inlineStr">
+        <is>
+          <t>Irena Korsake</t>
+        </is>
+      </c>
+      <c r="X298" s="2" t="inlineStr">
+        <is>
+          <t>Head of Purchasing</t>
+        </is>
+      </c>
+      <c r="Y298" s="2" t="inlineStr"/>
+      <c r="Z298" s="2" t="inlineStr"/>
+      <c r="AA298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/irena-korsake-572b8710b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Fallon &amp; Byrne Limited</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>Fallon &amp; Byrne Limited</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>8034</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>11-17 Exchequer Street</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>D02 RY63</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fallonandbyrne.com</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr"/>
+      <c r="K299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr"/>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>wine@fallonandbyrne.com</t>
+        </is>
+      </c>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 472 1010</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>393383</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fallon-&amp;-byrne/</t>
+        </is>
+      </c>
+      <c r="S299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/FallonandByrne/</t>
+        </is>
+      </c>
+      <c r="T299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/FallonandByrne/</t>
+        </is>
+      </c>
+      <c r="U299" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/fallonandbyrne</t>
+        </is>
+      </c>
+      <c r="V299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@fallonbyrne9920/</t>
+        </is>
+      </c>
+      <c r="W299" s="2" t="inlineStr">
+        <is>
+          <t>Donal Flynn</t>
+        </is>
+      </c>
+      <c r="X299" s="2" t="inlineStr">
+        <is>
+          <t>Wine Buyer</t>
+        </is>
+      </c>
+      <c r="Y299" s="2" t="inlineStr"/>
+      <c r="Z299" s="2" t="inlineStr"/>
+      <c r="AA299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/donal-flynn-b0a918119/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>The Drink Store Limited</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>The Drink Store Limited</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>8033</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 7</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>87 Manor Street, Stoneybatter</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>D07 A0Y2</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>https://drinkstore.ie</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr"/>
+      <c r="K300" s="2" t="inlineStr"/>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>info@drinkstore.ie</t>
+        </is>
+      </c>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 671 9760</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>313789</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="inlineStr"/>
+      <c r="S300" s="2" t="inlineStr"/>
+      <c r="T300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drinkstore.ie/</t>
+        </is>
+      </c>
+      <c r="U300" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/drinkstore</t>
+        </is>
+      </c>
+      <c r="V300" s="2" t="inlineStr"/>
+      <c r="W300" s="2" t="inlineStr">
+        <is>
+          <t>Ken Butler</t>
+        </is>
+      </c>
+      <c r="X300" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y300" s="2" t="inlineStr"/>
+      <c r="Z300" s="2" t="inlineStr"/>
+      <c r="AA300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ken-butler-1b670515/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Matson's Wine Store</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Matson's Wine Store</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>126143</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>County Cork</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>Cooney's Lane, Douglas</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>T12 HN2E</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.matsons.ie</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr"/>
+      <c r="K301" s="2" t="inlineStr"/>
+      <c r="L301" s="2" t="inlineStr"/>
+      <c r="M301" s="2" t="inlineStr"/>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>matsonswinestore@gmail.com</t>
+        </is>
+      </c>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 436 9577</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr"/>
+      <c r="Q301" s="2" t="inlineStr"/>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/matsons/</t>
+        </is>
+      </c>
+      <c r="S301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/matsons.store</t>
+        </is>
+      </c>
+      <c r="T301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/matsonswinestore/</t>
+        </is>
+      </c>
+      <c r="U301" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/matsonswines</t>
+        </is>
+      </c>
+      <c r="V301" s="2" t="inlineStr"/>
+      <c r="W301" s="2" t="inlineStr">
+        <is>
+          <t>Derrick Matson</t>
+        </is>
+      </c>
+      <c r="X301" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y301" s="2" t="inlineStr"/>
+      <c r="Z301" s="2" t="inlineStr"/>
+      <c r="AA301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/derrick-matson-a60a8b2a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Matson's Wine Store</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Matson's Wine Store</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>126143</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>County Cork</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>Cooney's Lane, Douglas</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>T12 HN2E</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.matsons.ie</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr"/>
+      <c r="K302" s="2" t="inlineStr"/>
+      <c r="L302" s="2" t="inlineStr"/>
+      <c r="M302" s="2" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>matsonswinestore@gmail.com</t>
+        </is>
+      </c>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>+353 21 436 9577</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr"/>
+      <c r="Q302" s="2" t="inlineStr"/>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/matsons/</t>
+        </is>
+      </c>
+      <c r="S302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/matsons.store</t>
+        </is>
+      </c>
+      <c r="T302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/matsonswinestore/</t>
+        </is>
+      </c>
+      <c r="U302" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/matsonswines</t>
+        </is>
+      </c>
+      <c r="V302" s="2" t="inlineStr"/>
+      <c r="W302" s="2" t="inlineStr">
+        <is>
+          <t>Alessia Frongillo</t>
+        </is>
+      </c>
+      <c r="X302" s="2" t="inlineStr">
+        <is>
+          <t>Wine Development Manager</t>
+        </is>
+      </c>
+      <c r="Y302" s="2" t="inlineStr"/>
+      <c r="Z302" s="2" t="inlineStr"/>
+      <c r="AA302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alessia-frongillo-634161242/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>The Corkscrew Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>The Corkscrew Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>8009</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>4 Harry Street</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>D02 CX24</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecorkscrew.ie</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr"/>
+      <c r="K303" s="2" t="inlineStr"/>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="inlineStr"/>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>sales@thecorkscrew.ie</t>
+        </is>
+      </c>
+      <c r="O303" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 674 5731</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q303" s="2" t="inlineStr"/>
+      <c r="R303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-corkscrew-wine-merchants-ireland/</t>
+        </is>
+      </c>
+      <c r="S303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thecorkscrew</t>
+        </is>
+      </c>
+      <c r="T303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thecorkscrewdublin/</t>
+        </is>
+      </c>
+      <c r="U303" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/corkscrewnation</t>
+        </is>
+      </c>
+      <c r="V303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@corkscrewdublin/</t>
+        </is>
+      </c>
+      <c r="W303" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Sutton</t>
+        </is>
+      </c>
+      <c r="X303" s="2" t="inlineStr">
+        <is>
+          <t>Spirits Manager</t>
+        </is>
+      </c>
+      <c r="Y303" s="2" t="inlineStr"/>
+      <c r="Z303" s="2" t="inlineStr"/>
+      <c r="AA303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomas-sutton-94bb60183/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>The Corkscrew Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>The Corkscrew Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>8009</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>4 Harry Street</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>D02 CX24</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecorkscrew.ie</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr"/>
+      <c r="K304" s="2" t="inlineStr"/>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr"/>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>sales@thecorkscrew.ie</t>
+        </is>
+      </c>
+      <c r="O304" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 674 5731</t>
+        </is>
+      </c>
+      <c r="P304" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q304" s="2" t="inlineStr"/>
+      <c r="R304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-corkscrew-wine-merchants-ireland/</t>
+        </is>
+      </c>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thecorkscrew</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thecorkscrewdublin/</t>
+        </is>
+      </c>
+      <c r="U304" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/corkscrewnation</t>
+        </is>
+      </c>
+      <c r="V304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@corkscrewdublin/</t>
+        </is>
+      </c>
+      <c r="W304" s="2" t="inlineStr">
+        <is>
+          <t>Peter Foley</t>
+        </is>
+      </c>
+      <c r="X304" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y304" s="2" t="inlineStr"/>
+      <c r="Z304" s="2" t="inlineStr"/>
+      <c r="AA304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-foley-26648447/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>Comans Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Comans Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>7968</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>Belgard Road</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>D22 R867</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comans.ie</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr"/>
+      <c r="K305" s="2" t="inlineStr"/>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr"/>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>info@comans.ie</t>
+        </is>
+      </c>
+      <c r="O305" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 466 2700</t>
+        </is>
+      </c>
+      <c r="P305" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>24049</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comans-wholesale</t>
+        </is>
+      </c>
+      <c r="S305" s="2" t="inlineStr"/>
+      <c r="T305" s="2" t="inlineStr"/>
+      <c r="U305" s="2" t="inlineStr"/>
+      <c r="V305" s="2" t="inlineStr"/>
+      <c r="W305" s="2" t="inlineStr">
+        <is>
+          <t>Tom Coman</t>
+        </is>
+      </c>
+      <c r="X305" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="Y305" s="2" t="inlineStr"/>
+      <c r="Z305" s="2" t="inlineStr"/>
+      <c r="AA305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tom-coman-9b715221/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Comans Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>Comans Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>7968</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>Belgard Road</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>D22 R867</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comans.ie</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr"/>
+      <c r="K306" s="2" t="inlineStr"/>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr"/>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>info@comans.ie</t>
+        </is>
+      </c>
+      <c r="O306" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 466 2700</t>
+        </is>
+      </c>
+      <c r="P306" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>24049</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comans-wholesale</t>
+        </is>
+      </c>
+      <c r="S306" s="2" t="inlineStr"/>
+      <c r="T306" s="2" t="inlineStr"/>
+      <c r="U306" s="2" t="inlineStr"/>
+      <c r="V306" s="2" t="inlineStr"/>
+      <c r="W306" s="2" t="inlineStr">
+        <is>
+          <t>David Orr</t>
+        </is>
+      </c>
+      <c r="X306" s="2" t="inlineStr">
+        <is>
+          <t>National Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y306" s="2" t="inlineStr"/>
+      <c r="Z306" s="2" t="inlineStr"/>
+      <c r="AA306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-orr-b6332023/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA306"/>
+  <dimension ref="A1:AA327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -34816,6 +34816,2095 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>28883</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 8</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>32 Cook Street</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>D14 F765</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>https://retrovino.com</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr"/>
+      <c r="K307" s="2" t="inlineStr"/>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr"/>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>info@retrovino.com</t>
+        </is>
+      </c>
+      <c r="O307" s="2" t="inlineStr"/>
+      <c r="P307" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q307" s="2" t="inlineStr"/>
+      <c r="R307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/retrovino.com/</t>
+        </is>
+      </c>
+      <c r="S307" s="2" t="inlineStr"/>
+      <c r="T307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/retrovino_sake</t>
+        </is>
+      </c>
+      <c r="U307" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/retrovino</t>
+        </is>
+      </c>
+      <c r="V307" s="2" t="inlineStr"/>
+      <c r="W307" s="2" t="inlineStr">
+        <is>
+          <t>Colly Murray</t>
+        </is>
+      </c>
+      <c r="X307" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y307" s="2" t="inlineStr"/>
+      <c r="Z307" s="2" t="inlineStr"/>
+      <c r="AA307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/collymurray/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr"/>
+      <c r="K308" s="2" t="inlineStr"/>
+      <c r="L308" s="2" t="inlineStr"/>
+      <c r="M308" s="2" t="inlineStr"/>
+      <c r="N308" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O308" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U308" s="2" t="inlineStr"/>
+      <c r="V308" s="2" t="inlineStr"/>
+      <c r="W308" s="2" t="inlineStr">
+        <is>
+          <t>Oana Cristina</t>
+        </is>
+      </c>
+      <c r="X308" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Officer</t>
+        </is>
+      </c>
+      <c r="Y308" s="2" t="inlineStr"/>
+      <c r="Z308" s="2" t="inlineStr"/>
+      <c r="AA308" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/stamatinoana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr"/>
+      <c r="K309" s="2" t="inlineStr"/>
+      <c r="L309" s="2" t="inlineStr"/>
+      <c r="M309" s="2" t="inlineStr"/>
+      <c r="N309" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O309" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P309" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U309" s="2" t="inlineStr"/>
+      <c r="V309" s="2" t="inlineStr"/>
+      <c r="W309" s="2" t="inlineStr">
+        <is>
+          <t>Alexandr Gazibar</t>
+        </is>
+      </c>
+      <c r="X309" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y309" s="2" t="inlineStr"/>
+      <c r="Z309" s="2" t="inlineStr"/>
+      <c r="AA309" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/alexandr-gazibar-8a424821a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr"/>
+      <c r="K310" s="2" t="inlineStr"/>
+      <c r="L310" s="2" t="inlineStr"/>
+      <c r="M310" s="2" t="inlineStr"/>
+      <c r="N310" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O310" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="inlineStr"/>
+      <c r="W310" s="2" t="inlineStr">
+        <is>
+          <t>Sergey Ternovskiy</t>
+        </is>
+      </c>
+      <c r="X310" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y310" s="2" t="inlineStr"/>
+      <c r="Z310" s="2" t="inlineStr"/>
+      <c r="AA310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sergey-ternovskiy-53763752/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>29607</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 3</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>48 Clontarf Road, Clontarf</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>D03 RR40</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clontarfwines.ie</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr"/>
+      <c r="K311" s="2" t="inlineStr"/>
+      <c r="L311" s="2" t="inlineStr"/>
+      <c r="M311" s="2" t="inlineStr"/>
+      <c r="N311" s="2" t="inlineStr">
+        <is>
+          <t>clontarfwines@gmail.com</t>
+        </is>
+      </c>
+      <c r="O311" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 853 3088</t>
+        </is>
+      </c>
+      <c r="P311" s="2" t="inlineStr"/>
+      <c r="Q311" s="2" t="inlineStr"/>
+      <c r="R311" s="2" t="inlineStr"/>
+      <c r="S311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/clontarf-wines-296283393843216/</t>
+        </is>
+      </c>
+      <c r="T311" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/clontarfwines</t>
+        </is>
+      </c>
+      <c r="U311" s="2" t="inlineStr"/>
+      <c r="V311" s="2" t="inlineStr"/>
+      <c r="W311" s="2" t="inlineStr">
+        <is>
+          <t>Ronnie Caraher</t>
+        </is>
+      </c>
+      <c r="X311" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y311" s="2" t="inlineStr"/>
+      <c r="Z311" s="2" t="inlineStr"/>
+      <c r="AA311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronnie-caraher-7b36ab113/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr"/>
+      <c r="K312" s="2" t="inlineStr"/>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr"/>
+      <c r="N312" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O312" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R312" s="2" t="inlineStr"/>
+      <c r="S312" s="2" t="inlineStr"/>
+      <c r="T312" s="2" t="inlineStr"/>
+      <c r="U312" s="2" t="inlineStr"/>
+      <c r="V312" s="2" t="inlineStr"/>
+      <c r="W312" s="2" t="inlineStr">
+        <is>
+          <t>William Doogan</t>
+        </is>
+      </c>
+      <c r="X312" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y312" s="2" t="inlineStr"/>
+      <c r="Z312" s="2" t="inlineStr"/>
+      <c r="AA312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-doogan-00b52540/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr"/>
+      <c r="K313" s="2" t="inlineStr"/>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr"/>
+      <c r="N313" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O313" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R313" s="2" t="inlineStr"/>
+      <c r="S313" s="2" t="inlineStr"/>
+      <c r="T313" s="2" t="inlineStr"/>
+      <c r="U313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="inlineStr"/>
+      <c r="W313" s="2" t="inlineStr">
+        <is>
+          <t>Paul Flynn</t>
+        </is>
+      </c>
+      <c r="X313" s="2" t="inlineStr">
+        <is>
+          <t>Sales Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y313" s="2" t="inlineStr"/>
+      <c r="Z313" s="2" t="inlineStr"/>
+      <c r="AA313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulflynnthewineguyni/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>54646</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Tralee</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>County Kerry</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>80 Boherbee, Cloonalour</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>V92 TW90</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>https://nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr"/>
+      <c r="K314" s="2" t="inlineStr"/>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr"/>
+      <c r="N314" s="2" t="inlineStr">
+        <is>
+          <t>info@nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="O314" s="2" t="inlineStr">
+        <is>
+          <t>+353 66 718 0360</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>65599</t>
+        </is>
+      </c>
+      <c r="R314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/castle-off-licence/</t>
+        </is>
+      </c>
+      <c r="S314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/castleofflicence</t>
+        </is>
+      </c>
+      <c r="T314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/castle.offy.tralee/</t>
+        </is>
+      </c>
+      <c r="U314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="inlineStr"/>
+      <c r="W314" s="2" t="inlineStr">
+        <is>
+          <t>Fiona Palfrey</t>
+        </is>
+      </c>
+      <c r="X314" s="2" t="inlineStr">
+        <is>
+          <t>General Manager/ Director</t>
+        </is>
+      </c>
+      <c r="Y314" s="2" t="inlineStr"/>
+      <c r="Z314" s="2" t="inlineStr"/>
+      <c r="AA314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fiona-palfrey-46825722</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>8060</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Galway</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>County Galway</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>3 Middle Street Mews, Middle Street</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>H91 C2V4</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr"/>
+      <c r="K315" s="2" t="inlineStr"/>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="inlineStr"/>
+      <c r="N315" s="2" t="inlineStr">
+        <is>
+          <t>info@woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="O315" s="2" t="inlineStr">
+        <is>
+          <t>+353 91 533 706</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="Q315" s="2" t="inlineStr"/>
+      <c r="R315" s="2" t="inlineStr"/>
+      <c r="S315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/woodberrys</t>
+        </is>
+      </c>
+      <c r="T315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woodberrywines/</t>
+        </is>
+      </c>
+      <c r="U315" s="2" t="inlineStr"/>
+      <c r="V315" s="2" t="inlineStr"/>
+      <c r="W315" s="2" t="inlineStr"/>
+      <c r="X315" s="2" t="inlineStr"/>
+      <c r="Y315" s="2" t="inlineStr"/>
+      <c r="Z315" s="2" t="inlineStr"/>
+      <c r="AA315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr"/>
+      <c r="K316" s="2" t="inlineStr"/>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr"/>
+      <c r="N316" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O316" s="2" t="inlineStr"/>
+      <c r="P316" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R316" s="2" t="inlineStr"/>
+      <c r="S316" s="2" t="inlineStr"/>
+      <c r="T316" s="2" t="inlineStr"/>
+      <c r="U316" s="2" t="inlineStr"/>
+      <c r="V316" s="2" t="inlineStr"/>
+      <c r="W316" s="2" t="inlineStr">
+        <is>
+          <t>John Donohoe</t>
+        </is>
+      </c>
+      <c r="X316" s="2" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="Y316" s="2" t="inlineStr"/>
+      <c r="Z316" s="2" t="inlineStr"/>
+      <c r="AA316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-donohoe-48a5a33b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr"/>
+      <c r="K317" s="2" t="inlineStr"/>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr"/>
+      <c r="N317" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O317" s="2" t="inlineStr"/>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R317" s="2" t="inlineStr"/>
+      <c r="S317" s="2" t="inlineStr"/>
+      <c r="T317" s="2" t="inlineStr"/>
+      <c r="U317" s="2" t="inlineStr"/>
+      <c r="V317" s="2" t="inlineStr"/>
+      <c r="W317" s="2" t="inlineStr">
+        <is>
+          <t>James O’hara</t>
+        </is>
+      </c>
+      <c r="X317" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y317" s="2" t="inlineStr"/>
+      <c r="Z317" s="2" t="inlineStr"/>
+      <c r="AA317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-o-hara-45a93138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr"/>
+      <c r="K318" s="2" t="inlineStr"/>
+      <c r="L318" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="inlineStr"/>
+      <c r="N318" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O318" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P318" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U318" s="2" t="inlineStr"/>
+      <c r="V318" s="2" t="inlineStr"/>
+      <c r="W318" s="2" t="inlineStr">
+        <is>
+          <t>Marilia Carraro</t>
+        </is>
+      </c>
+      <c r="X318" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y318" s="2" t="inlineStr"/>
+      <c r="Z318" s="2" t="inlineStr"/>
+      <c r="AA318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mariliacarraro/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr"/>
+      <c r="K319" s="2" t="inlineStr"/>
+      <c r="L319" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="inlineStr"/>
+      <c r="N319" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O319" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q319" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U319" s="2" t="inlineStr"/>
+      <c r="V319" s="2" t="inlineStr"/>
+      <c r="W319" s="2" t="inlineStr">
+        <is>
+          <t>Piero Murgia</t>
+        </is>
+      </c>
+      <c r="X319" s="2" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y319" s="2" t="inlineStr"/>
+      <c r="Z319" s="2" t="inlineStr"/>
+      <c r="AA319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/piero-murgia-313003150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr"/>
+      <c r="K320" s="2" t="inlineStr"/>
+      <c r="L320" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="inlineStr"/>
+      <c r="N320" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O320" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U320" s="2" t="inlineStr"/>
+      <c r="V320" s="2" t="inlineStr"/>
+      <c r="W320" s="2" t="inlineStr">
+        <is>
+          <t>Daragh Monahan</t>
+        </is>
+      </c>
+      <c r="X320" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Sales</t>
+        </is>
+      </c>
+      <c r="Y320" s="2" t="inlineStr"/>
+      <c r="Z320" s="2" t="inlineStr"/>
+      <c r="AA320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daragh-monahan-4716881a3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr"/>
+      <c r="K321" s="2" t="inlineStr"/>
+      <c r="L321" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="inlineStr"/>
+      <c r="N321" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O321" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q321" s="2" t="inlineStr"/>
+      <c r="R321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U321" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V321" s="2" t="inlineStr"/>
+      <c r="W321" s="2" t="inlineStr">
+        <is>
+          <t>Avril Kirrane</t>
+        </is>
+      </c>
+      <c r="X321" s="2" t="inlineStr">
+        <is>
+          <t>Wine Specialist &amp; Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y321" s="2" t="inlineStr"/>
+      <c r="Z321" s="2" t="inlineStr"/>
+      <c r="AA321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avril-kirrane-42055115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr"/>
+      <c r="K322" s="2" t="inlineStr"/>
+      <c r="L322" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="inlineStr"/>
+      <c r="N322" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O322" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q322" s="2" t="inlineStr"/>
+      <c r="R322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U322" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V322" s="2" t="inlineStr"/>
+      <c r="W322" s="2" t="inlineStr">
+        <is>
+          <t>Johnny Mcmorrough</t>
+        </is>
+      </c>
+      <c r="X322" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y322" s="2" t="inlineStr"/>
+      <c r="Z322" s="2" t="inlineStr"/>
+      <c r="AA322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johnny-mcmorrough-32597a3a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Kilkenny</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>Co. Kilkenny</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>Market Yard</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>R95 FH05</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>https://lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr"/>
+      <c r="K323" s="2" t="inlineStr"/>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr"/>
+      <c r="N323" s="2" t="inlineStr">
+        <is>
+          <t>orders@lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="O323" s="2" t="inlineStr">
+        <is>
+          <t>+353 56 775 2166</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>311736</t>
+        </is>
+      </c>
+      <c r="R323" s="2" t="inlineStr"/>
+      <c r="S323" s="2" t="inlineStr"/>
+      <c r="T323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lecaveauwinemerchants</t>
+        </is>
+      </c>
+      <c r="U323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="inlineStr"/>
+      <c r="W323" s="2" t="inlineStr">
+        <is>
+          <t>Pascal Rossignol</t>
+        </is>
+      </c>
+      <c r="X323" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Owner</t>
+        </is>
+      </c>
+      <c r="Y323" s="2" t="inlineStr"/>
+      <c r="Z323" s="2" t="inlineStr"/>
+      <c r="AA323" s="2" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>23827</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>Co. Louth</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>Williamson's Mall, Francis Street, Townparks</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>A91 NR29</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr"/>
+      <c r="K324" s="2" t="inlineStr"/>
+      <c r="L324" s="2" t="inlineStr"/>
+      <c r="M324" s="2" t="inlineStr"/>
+      <c r="N324" s="2" t="inlineStr">
+        <is>
+          <t>info@dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="O324" s="2" t="inlineStr"/>
+      <c r="P324" s="2" t="inlineStr"/>
+      <c r="Q324" s="2" t="inlineStr"/>
+      <c r="R324" s="2" t="inlineStr"/>
+      <c r="S324" s="2" t="inlineStr"/>
+      <c r="T324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/macguinnesswine/</t>
+        </is>
+      </c>
+      <c r="U324" s="2" t="inlineStr"/>
+      <c r="V324" s="2" t="inlineStr"/>
+      <c r="W324" s="2" t="inlineStr">
+        <is>
+          <t>Alan Mac Guinness Rockwines</t>
+        </is>
+      </c>
+      <c r="X324" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y324" s="2" t="inlineStr"/>
+      <c r="Z324" s="2" t="inlineStr"/>
+      <c r="AA324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alan-mac-guinness-rockwines-69839624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>42229</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>117 Philipsburgh Avenue, Fairview</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>D03 XV04</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>https://sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr"/>
+      <c r="K325" s="2" t="inlineStr"/>
+      <c r="L325" s="2" t="inlineStr"/>
+      <c r="M325" s="2" t="inlineStr"/>
+      <c r="N325" s="2" t="inlineStr">
+        <is>
+          <t>info@sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="O325" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 837 2857</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="inlineStr"/>
+      <c r="Q325" s="2" t="inlineStr"/>
+      <c r="R325" s="2" t="inlineStr"/>
+      <c r="S325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Sweeneysd3/</t>
+        </is>
+      </c>
+      <c r="T325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="U325" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="V325" s="2" t="inlineStr"/>
+      <c r="W325" s="2" t="inlineStr"/>
+      <c r="X325" s="2" t="inlineStr"/>
+      <c r="Y325" s="2" t="inlineStr"/>
+      <c r="Z325" s="2" t="inlineStr"/>
+      <c r="AA325" s="2" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>46310</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>Carry Out Tyrellstown, Unit 7 The Plaza, Tyrellstown Town Centre, Tyrrelstown</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>D15 XF21</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecru.ie</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr"/>
+      <c r="K326" s="2" t="inlineStr"/>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr"/>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>Orders@TheCru.ie</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 485 3171</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q326" s="2" t="inlineStr"/>
+      <c r="R326" s="2" t="inlineStr"/>
+      <c r="S326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com//thecru.ie</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thecru.ie</t>
+        </is>
+      </c>
+      <c r="U326" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCru_IE</t>
+        </is>
+      </c>
+      <c r="V326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCNRk_PWRb3yOQK77FxGVe6g/featured</t>
+        </is>
+      </c>
+      <c r="W326" s="2" t="inlineStr"/>
+      <c r="X326" s="2" t="inlineStr"/>
+      <c r="Y326" s="2" t="inlineStr"/>
+      <c r="Z326" s="2" t="inlineStr"/>
+      <c r="AA326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>21158</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>25 Ranelagh, Ranelagh</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>D06 RP40</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.redmonds.ie</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr"/>
+      <c r="K327" s="2" t="inlineStr"/>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr"/>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>info@redmonds.ie</t>
+        </is>
+      </c>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 496 0552</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>51847</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="inlineStr"/>
+      <c r="S327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/redmonds-off-licence-ranelagh-120637134043/</t>
+        </is>
+      </c>
+      <c r="T327" s="2" t="inlineStr">
+        <is>
+          <t>http://instagram.com/redmondsd6</t>
+        </is>
+      </c>
+      <c r="U327" s="2" t="inlineStr"/>
+      <c r="V327" s="2" t="inlineStr"/>
+      <c r="W327" s="2" t="inlineStr"/>
+      <c r="X327" s="2" t="inlineStr"/>
+      <c r="Y327" s="2" t="inlineStr"/>
+      <c r="Z327" s="2" t="inlineStr"/>
+      <c r="AA327" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA327"/>
+  <dimension ref="A1:AA354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -36905,6 +36905,2649 @@
       <c r="Z327" s="2" t="inlineStr"/>
       <c r="AA327" s="2" t="inlineStr"/>
     </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Green Man Wines</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>Green Man Wines</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>48604</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 6W</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>3 Terenure Road North</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>D6W PY04</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greenmanwines.ie</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr"/>
+      <c r="K328" s="2" t="inlineStr"/>
+      <c r="L328" s="2" t="inlineStr"/>
+      <c r="M328" s="2" t="inlineStr"/>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>info@greenmanwines.ie</t>
+        </is>
+      </c>
+      <c r="O328" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 559 4234</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="inlineStr"/>
+      <c r="Q328" s="2" t="inlineStr"/>
+      <c r="R328" s="2" t="inlineStr"/>
+      <c r="S328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GreenManWines</t>
+        </is>
+      </c>
+      <c r="T328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/green_man_wines</t>
+        </is>
+      </c>
+      <c r="U328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr"/>
+      <c r="W328" s="2" t="inlineStr">
+        <is>
+          <t>David Gallagher</t>
+        </is>
+      </c>
+      <c r="X328" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Director</t>
+        </is>
+      </c>
+      <c r="Y328" s="2" t="inlineStr"/>
+      <c r="Z328" s="2" t="inlineStr"/>
+      <c r="AA328" s="2" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr"/>
+      <c r="K329" s="2" t="inlineStr"/>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr"/>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O329" s="2" t="inlineStr"/>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr"/>
+      <c r="S329" s="2" t="inlineStr"/>
+      <c r="T329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U329" s="2" t="inlineStr"/>
+      <c r="V329" s="2" t="inlineStr"/>
+      <c r="W329" s="2" t="inlineStr">
+        <is>
+          <t>Jennifer Thompson</t>
+        </is>
+      </c>
+      <c r="X329" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y329" s="2" t="inlineStr"/>
+      <c r="Z329" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr"/>
+      <c r="K330" s="2" t="inlineStr"/>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O330" s="2" t="inlineStr"/>
+      <c r="P330" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr"/>
+      <c r="S330" s="2" t="inlineStr"/>
+      <c r="T330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U330" s="2" t="inlineStr"/>
+      <c r="V330" s="2" t="inlineStr"/>
+      <c r="W330" s="2" t="inlineStr">
+        <is>
+          <t>Anne Rodgers</t>
+        </is>
+      </c>
+      <c r="X330" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y330" s="2" t="inlineStr"/>
+      <c r="Z330" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA330" s="2" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>39954</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>26 Pembroke Street Upper</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>D02 X361</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>https://grapecircus.ie, https://www.grapecircus.com</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr"/>
+      <c r="K331" s="2" t="inlineStr"/>
+      <c r="L331" s="2" t="inlineStr"/>
+      <c r="M331" s="2" t="inlineStr"/>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>grapecircus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O331" s="2" t="inlineStr"/>
+      <c r="P331" s="2" t="inlineStr"/>
+      <c r="Q331" s="2" t="inlineStr"/>
+      <c r="R331" s="2" t="inlineStr"/>
+      <c r="S331" s="2" t="inlineStr"/>
+      <c r="T331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grapecircus</t>
+        </is>
+      </c>
+      <c r="U331" s="2" t="inlineStr"/>
+      <c r="V331" s="2" t="inlineStr"/>
+      <c r="W331" s="2" t="inlineStr">
+        <is>
+          <t>Enrico Fantasia</t>
+        </is>
+      </c>
+      <c r="X331" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y331" s="2" t="inlineStr"/>
+      <c r="Z331" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/enrico-fantasia-247b4838/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>39954</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>26 Pembroke Street Upper</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>D02 X361</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>https://grapecircus.ie, https://www.grapecircus.com</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr"/>
+      <c r="K332" s="2" t="inlineStr"/>
+      <c r="L332" s="2" t="inlineStr"/>
+      <c r="M332" s="2" t="inlineStr"/>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>grapecircus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr"/>
+      <c r="P332" s="2" t="inlineStr"/>
+      <c r="Q332" s="2" t="inlineStr"/>
+      <c r="R332" s="2" t="inlineStr"/>
+      <c r="S332" s="2" t="inlineStr"/>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grapecircus</t>
+        </is>
+      </c>
+      <c r="U332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="inlineStr"/>
+      <c r="W332" s="2" t="inlineStr">
+        <is>
+          <t>Philippa Moore</t>
+        </is>
+      </c>
+      <c r="X332" s="2" t="inlineStr">
+        <is>
+          <t>In Charge</t>
+        </is>
+      </c>
+      <c r="Y332" s="2" t="inlineStr"/>
+      <c r="Z332" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA332" s="2" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Enowine</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>Enowine</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Co. Meath</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>Unit 14, East Mullaghboy Industrial Estate</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>C15 C603</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>https://enowine.ie</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr"/>
+      <c r="K333" s="2" t="inlineStr"/>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr"/>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>info@enowine.ie</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr">
+        <is>
+          <t>+353 46 907 3613</t>
+        </is>
+      </c>
+      <c r="P333" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>8526</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr"/>
+      <c r="S333" s="2" t="inlineStr"/>
+      <c r="T333" s="2" t="inlineStr"/>
+      <c r="U333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="inlineStr"/>
+      <c r="W333" s="2" t="inlineStr">
+        <is>
+          <t>Damien Brennan</t>
+        </is>
+      </c>
+      <c r="X333" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y333" s="2" t="inlineStr"/>
+      <c r="Z333" s="2" t="inlineStr"/>
+      <c r="AA333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/damien-brennan-007825135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>28883</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 8</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>32 Cook Street</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>D14 F765</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>https://retrovino.com</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr"/>
+      <c r="K334" s="2" t="inlineStr"/>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr"/>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>info@retrovino.com</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr"/>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q334" s="2" t="inlineStr"/>
+      <c r="R334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/retrovino.com/</t>
+        </is>
+      </c>
+      <c r="S334" s="2" t="inlineStr"/>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/retrovino_sake</t>
+        </is>
+      </c>
+      <c r="U334" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/retrovino</t>
+        </is>
+      </c>
+      <c r="V334" s="2" t="inlineStr"/>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>Colly Murray</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y334" s="2" t="inlineStr"/>
+      <c r="Z334" s="2" t="inlineStr"/>
+      <c r="AA334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/collymurray/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr"/>
+      <c r="K335" s="2" t="inlineStr"/>
+      <c r="L335" s="2" t="inlineStr"/>
+      <c r="M335" s="2" t="inlineStr"/>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr"/>
+      <c r="W335" s="2" t="inlineStr">
+        <is>
+          <t>Oana Cristina</t>
+        </is>
+      </c>
+      <c r="X335" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Officer</t>
+        </is>
+      </c>
+      <c r="Y335" s="2" t="inlineStr"/>
+      <c r="Z335" s="2" t="inlineStr"/>
+      <c r="AA335" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/stamatinoana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr"/>
+      <c r="L336" s="2" t="inlineStr"/>
+      <c r="M336" s="2" t="inlineStr"/>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O336" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U336" s="2" t="inlineStr"/>
+      <c r="V336" s="2" t="inlineStr"/>
+      <c r="W336" s="2" t="inlineStr">
+        <is>
+          <t>Sergey Ternovskiy</t>
+        </is>
+      </c>
+      <c r="X336" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y336" s="2" t="inlineStr"/>
+      <c r="Z336" s="2" t="inlineStr"/>
+      <c r="AA336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sergey-ternovskiy-53763752/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr"/>
+      <c r="K337" s="2" t="inlineStr"/>
+      <c r="L337" s="2" t="inlineStr"/>
+      <c r="M337" s="2" t="inlineStr"/>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U337" s="2" t="inlineStr"/>
+      <c r="V337" s="2" t="inlineStr"/>
+      <c r="W337" s="2" t="inlineStr">
+        <is>
+          <t>Alexandr Gazibar</t>
+        </is>
+      </c>
+      <c r="X337" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y337" s="2" t="inlineStr"/>
+      <c r="Z337" s="2" t="inlineStr"/>
+      <c r="AA337" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/alexandr-gazibar-8a424821a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>29607</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 3</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>48 Clontarf Road, Clontarf</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>D03 RR40</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clontarfwines.ie</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr"/>
+      <c r="M338" s="2" t="inlineStr"/>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>clontarfwines@gmail.com</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 853 3088</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="inlineStr"/>
+      <c r="Q338" s="2" t="inlineStr"/>
+      <c r="R338" s="2" t="inlineStr"/>
+      <c r="S338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/clontarf-wines-296283393843216/</t>
+        </is>
+      </c>
+      <c r="T338" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/clontarfwines</t>
+        </is>
+      </c>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr"/>
+      <c r="W338" s="2" t="inlineStr">
+        <is>
+          <t>Ronnie Caraher</t>
+        </is>
+      </c>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronnie-caraher-7b36ab113/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr"/>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr"/>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr"/>
+      <c r="S339" s="2" t="inlineStr"/>
+      <c r="T339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr"/>
+      <c r="W339" s="2" t="inlineStr">
+        <is>
+          <t>William Doogan</t>
+        </is>
+      </c>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-doogan-00b52540/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr"/>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr"/>
+      <c r="S340" s="2" t="inlineStr"/>
+      <c r="T340" s="2" t="inlineStr"/>
+      <c r="U340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="inlineStr"/>
+      <c r="W340" s="2" t="inlineStr">
+        <is>
+          <t>Paul Flynn</t>
+        </is>
+      </c>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>Sales Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr"/>
+      <c r="AA340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulflynnthewineguyni/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>54646</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>Tralee</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>County Kerry</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>80 Boherbee, Cloonalour</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>V92 TW90</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>https://nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr"/>
+      <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr"/>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>info@nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>+353 66 718 0360</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>65599</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/castle-off-licence/</t>
+        </is>
+      </c>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/castleofflicence</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/castle.offy.tralee/</t>
+        </is>
+      </c>
+      <c r="U341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="inlineStr"/>
+      <c r="W341" s="2" t="inlineStr">
+        <is>
+          <t>Fiona Palfrey</t>
+        </is>
+      </c>
+      <c r="X341" s="2" t="inlineStr">
+        <is>
+          <t>General Manager/ Director</t>
+        </is>
+      </c>
+      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Z341" s="2" t="inlineStr"/>
+      <c r="AA341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fiona-palfrey-46825722</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>8060</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>Galway</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>County Galway</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>3 Middle Street Mews, Middle Street</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>H91 C2V4</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr"/>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr"/>
+      <c r="N342" s="2" t="inlineStr">
+        <is>
+          <t>info@woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>+353 91 533 706</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="Q342" s="2" t="inlineStr"/>
+      <c r="R342" s="2" t="inlineStr"/>
+      <c r="S342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/woodberrys</t>
+        </is>
+      </c>
+      <c r="T342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woodberrywines/</t>
+        </is>
+      </c>
+      <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr"/>
+      <c r="W342" s="2" t="inlineStr"/>
+      <c r="X342" s="2" t="inlineStr"/>
+      <c r="Y342" s="2" t="inlineStr"/>
+      <c r="Z342" s="2" t="inlineStr"/>
+      <c r="AA342" s="2" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr"/>
+      <c r="K343" s="2" t="inlineStr"/>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr"/>
+      <c r="N343" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O343" s="2" t="inlineStr"/>
+      <c r="P343" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr"/>
+      <c r="S343" s="2" t="inlineStr"/>
+      <c r="T343" s="2" t="inlineStr"/>
+      <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr"/>
+      <c r="W343" s="2" t="inlineStr">
+        <is>
+          <t>John Donohoe</t>
+        </is>
+      </c>
+      <c r="X343" s="2" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="Y343" s="2" t="inlineStr"/>
+      <c r="Z343" s="2" t="inlineStr"/>
+      <c r="AA343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-donohoe-48a5a33b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr"/>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr"/>
+      <c r="N344" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr"/>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr"/>
+      <c r="S344" s="2" t="inlineStr"/>
+      <c r="T344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="inlineStr"/>
+      <c r="V344" s="2" t="inlineStr"/>
+      <c r="W344" s="2" t="inlineStr">
+        <is>
+          <t>James O’hara</t>
+        </is>
+      </c>
+      <c r="X344" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y344" s="2" t="inlineStr"/>
+      <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-o-hara-45a93138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr"/>
+      <c r="K345" s="2" t="inlineStr"/>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr"/>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U345" s="2" t="inlineStr"/>
+      <c r="V345" s="2" t="inlineStr"/>
+      <c r="W345" s="2" t="inlineStr">
+        <is>
+          <t>Marilia Carraro</t>
+        </is>
+      </c>
+      <c r="X345" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y345" s="2" t="inlineStr"/>
+      <c r="Z345" s="2" t="inlineStr"/>
+      <c r="AA345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mariliacarraro/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr"/>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr"/>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr"/>
+      <c r="W346" s="2" t="inlineStr">
+        <is>
+          <t>Piero Murgia</t>
+        </is>
+      </c>
+      <c r="X346" s="2" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y346" s="2" t="inlineStr"/>
+      <c r="Z346" s="2" t="inlineStr"/>
+      <c r="AA346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/piero-murgia-313003150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr"/>
+      <c r="K347" s="2" t="inlineStr"/>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr"/>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr"/>
+      <c r="W347" s="2" t="inlineStr">
+        <is>
+          <t>Daragh Monahan</t>
+        </is>
+      </c>
+      <c r="X347" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Sales</t>
+        </is>
+      </c>
+      <c r="Y347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr"/>
+      <c r="AA347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daragh-monahan-4716881a3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr"/>
+      <c r="K348" s="2" t="inlineStr"/>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr"/>
+      <c r="N348" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O348" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q348" s="2" t="inlineStr"/>
+      <c r="R348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U348" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V348" s="2" t="inlineStr"/>
+      <c r="W348" s="2" t="inlineStr">
+        <is>
+          <t>Avril Kirrane</t>
+        </is>
+      </c>
+      <c r="X348" s="2" t="inlineStr">
+        <is>
+          <t>Wine Specialist &amp; Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y348" s="2" t="inlineStr"/>
+      <c r="Z348" s="2" t="inlineStr"/>
+      <c r="AA348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avril-kirrane-42055115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr"/>
+      <c r="K349" s="2" t="inlineStr"/>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr"/>
+      <c r="N349" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O349" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q349" s="2" t="inlineStr"/>
+      <c r="R349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U349" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V349" s="2" t="inlineStr"/>
+      <c r="W349" s="2" t="inlineStr">
+        <is>
+          <t>Johnny Mcmorrough</t>
+        </is>
+      </c>
+      <c r="X349" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y349" s="2" t="inlineStr"/>
+      <c r="Z349" s="2" t="inlineStr"/>
+      <c r="AA349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johnny-mcmorrough-32597a3a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>Kilkenny</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Co. Kilkenny</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>Market Yard</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>R95 FH05</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>https://lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr"/>
+      <c r="K350" s="2" t="inlineStr"/>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr"/>
+      <c r="N350" s="2" t="inlineStr">
+        <is>
+          <t>orders@lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>+353 56 775 2166</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>311736</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="inlineStr"/>
+      <c r="S350" s="2" t="inlineStr"/>
+      <c r="T350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lecaveauwinemerchants</t>
+        </is>
+      </c>
+      <c r="U350" s="2" t="inlineStr"/>
+      <c r="V350" s="2" t="inlineStr"/>
+      <c r="W350" s="2" t="inlineStr">
+        <is>
+          <t>Pascal Rossignol</t>
+        </is>
+      </c>
+      <c r="X350" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Owner</t>
+        </is>
+      </c>
+      <c r="Y350" s="2" t="inlineStr"/>
+      <c r="Z350" s="2" t="inlineStr"/>
+      <c r="AA350" s="2" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>23827</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>Co. Louth</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>Williamson's Mall, Francis Street, Townparks</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>A91 NR29</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr"/>
+      <c r="K351" s="2" t="inlineStr"/>
+      <c r="L351" s="2" t="inlineStr"/>
+      <c r="M351" s="2" t="inlineStr"/>
+      <c r="N351" s="2" t="inlineStr">
+        <is>
+          <t>info@dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="O351" s="2" t="inlineStr"/>
+      <c r="P351" s="2" t="inlineStr"/>
+      <c r="Q351" s="2" t="inlineStr"/>
+      <c r="R351" s="2" t="inlineStr"/>
+      <c r="S351" s="2" t="inlineStr"/>
+      <c r="T351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/macguinnesswine/</t>
+        </is>
+      </c>
+      <c r="U351" s="2" t="inlineStr"/>
+      <c r="V351" s="2" t="inlineStr"/>
+      <c r="W351" s="2" t="inlineStr">
+        <is>
+          <t>Alan Mac Guinness Rockwines</t>
+        </is>
+      </c>
+      <c r="X351" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y351" s="2" t="inlineStr"/>
+      <c r="Z351" s="2" t="inlineStr"/>
+      <c r="AA351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alan-mac-guinness-rockwines-69839624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>42229</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>117 Philipsburgh Avenue, Fairview</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>D03 XV04</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>https://sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr"/>
+      <c r="K352" s="2" t="inlineStr"/>
+      <c r="L352" s="2" t="inlineStr"/>
+      <c r="M352" s="2" t="inlineStr"/>
+      <c r="N352" s="2" t="inlineStr">
+        <is>
+          <t>info@sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 837 2857</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr"/>
+      <c r="Q352" s="2" t="inlineStr"/>
+      <c r="R352" s="2" t="inlineStr"/>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Sweeneysd3/</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="U352" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="V352" s="2" t="inlineStr"/>
+      <c r="W352" s="2" t="inlineStr"/>
+      <c r="X352" s="2" t="inlineStr"/>
+      <c r="Y352" s="2" t="inlineStr"/>
+      <c r="Z352" s="2" t="inlineStr"/>
+      <c r="AA352" s="2" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>46310</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>Carry Out Tyrellstown, Unit 7 The Plaza, Tyrellstown Town Centre, Tyrrelstown</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>D15 XF21</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecru.ie</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr"/>
+      <c r="K353" s="2" t="inlineStr"/>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr"/>
+      <c r="N353" s="2" t="inlineStr">
+        <is>
+          <t>Orders@TheCru.ie</t>
+        </is>
+      </c>
+      <c r="O353" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 485 3171</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q353" s="2" t="inlineStr"/>
+      <c r="R353" s="2" t="inlineStr"/>
+      <c r="S353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com//thecru.ie</t>
+        </is>
+      </c>
+      <c r="T353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thecru.ie</t>
+        </is>
+      </c>
+      <c r="U353" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCru_IE</t>
+        </is>
+      </c>
+      <c r="V353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCNRk_PWRb3yOQK77FxGVe6g/featured</t>
+        </is>
+      </c>
+      <c r="W353" s="2" t="inlineStr"/>
+      <c r="X353" s="2" t="inlineStr"/>
+      <c r="Y353" s="2" t="inlineStr"/>
+      <c r="Z353" s="2" t="inlineStr"/>
+      <c r="AA353" s="2" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>21158</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>25 Ranelagh, Ranelagh</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>D06 RP40</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.redmonds.ie</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr"/>
+      <c r="K354" s="2" t="inlineStr"/>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr"/>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>info@redmonds.ie</t>
+        </is>
+      </c>
+      <c r="O354" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 496 0552</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>51847</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr"/>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/redmonds-off-licence-ranelagh-120637134043/</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="inlineStr">
+        <is>
+          <t>http://instagram.com/redmondsd6</t>
+        </is>
+      </c>
+      <c r="U354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="inlineStr"/>
+      <c r="W354" s="2" t="inlineStr"/>
+      <c r="X354" s="2" t="inlineStr"/>
+      <c r="Y354" s="2" t="inlineStr"/>
+      <c r="Z354" s="2" t="inlineStr"/>
+      <c r="AA354" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA354"/>
+  <dimension ref="A1:AA382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39548,6 +39548,2750 @@
       <c r="Z354" s="2" t="inlineStr"/>
       <c r="AA354" s="2" t="inlineStr"/>
     </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr"/>
+      <c r="K355" s="2" t="inlineStr"/>
+      <c r="L355" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="inlineStr"/>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr"/>
+      <c r="P355" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="inlineStr"/>
+      <c r="S355" s="2" t="inlineStr"/>
+      <c r="T355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U355" s="2" t="inlineStr"/>
+      <c r="V355" s="2" t="inlineStr"/>
+      <c r="W355" s="2" t="inlineStr">
+        <is>
+          <t>Jennifer Thompson</t>
+        </is>
+      </c>
+      <c r="X355" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y355" s="2" t="inlineStr"/>
+      <c r="Z355" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA355" s="2" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr"/>
+      <c r="K356" s="2" t="inlineStr"/>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr"/>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O356" s="2" t="inlineStr"/>
+      <c r="P356" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr"/>
+      <c r="S356" s="2" t="inlineStr"/>
+      <c r="T356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U356" s="2" t="inlineStr"/>
+      <c r="V356" s="2" t="inlineStr"/>
+      <c r="W356" s="2" t="inlineStr">
+        <is>
+          <t>Luis Solé Garriz</t>
+        </is>
+      </c>
+      <c r="X356" s="2" t="inlineStr">
+        <is>
+          <t>Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y356" s="2" t="inlineStr"/>
+      <c r="Z356" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-sole-garriz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr"/>
+      <c r="K357" s="2" t="inlineStr"/>
+      <c r="L357" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="inlineStr"/>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr"/>
+      <c r="P357" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="inlineStr"/>
+      <c r="S357" s="2" t="inlineStr"/>
+      <c r="T357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U357" s="2" t="inlineStr"/>
+      <c r="V357" s="2" t="inlineStr"/>
+      <c r="W357" s="2" t="inlineStr">
+        <is>
+          <t>Anne Rodgers</t>
+        </is>
+      </c>
+      <c r="X357" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y357" s="2" t="inlineStr"/>
+      <c r="Z357" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA357" s="2" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>Green Man Wines</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>Green Man Wines</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>48604</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 6W</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>3 Terenure Road North</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>D6W PY04</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greenmanwines.ie</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr"/>
+      <c r="K358" s="2" t="inlineStr"/>
+      <c r="L358" s="2" t="inlineStr"/>
+      <c r="M358" s="2" t="inlineStr"/>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>info@greenmanwines.ie</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 559 4234</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="inlineStr"/>
+      <c r="Q358" s="2" t="inlineStr"/>
+      <c r="R358" s="2" t="inlineStr"/>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GreenManWines</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/green_man_wines</t>
+        </is>
+      </c>
+      <c r="U358" s="2" t="inlineStr"/>
+      <c r="V358" s="2" t="inlineStr"/>
+      <c r="W358" s="2" t="inlineStr">
+        <is>
+          <t>David Gallagher</t>
+        </is>
+      </c>
+      <c r="X358" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Director</t>
+        </is>
+      </c>
+      <c r="Y358" s="2" t="inlineStr"/>
+      <c r="Z358" s="2" t="inlineStr"/>
+      <c r="AA358" s="2" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>39954</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>26 Pembroke Street Upper</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>D02 X361</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>https://grapecircus.ie, https://www.grapecircus.com</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr"/>
+      <c r="K359" s="2" t="inlineStr"/>
+      <c r="L359" s="2" t="inlineStr"/>
+      <c r="M359" s="2" t="inlineStr"/>
+      <c r="N359" s="2" t="inlineStr">
+        <is>
+          <t>grapecircus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O359" s="2" t="inlineStr"/>
+      <c r="P359" s="2" t="inlineStr"/>
+      <c r="Q359" s="2" t="inlineStr"/>
+      <c r="R359" s="2" t="inlineStr"/>
+      <c r="S359" s="2" t="inlineStr"/>
+      <c r="T359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grapecircus</t>
+        </is>
+      </c>
+      <c r="U359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="inlineStr"/>
+      <c r="W359" s="2" t="inlineStr">
+        <is>
+          <t>Enrico Fantasia</t>
+        </is>
+      </c>
+      <c r="X359" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y359" s="2" t="inlineStr"/>
+      <c r="Z359" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/enrico-fantasia-247b4838/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>39954</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>26 Pembroke Street Upper</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>D02 X361</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>https://grapecircus.ie, https://www.grapecircus.com</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr"/>
+      <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="2" t="inlineStr"/>
+      <c r="M360" s="2" t="inlineStr"/>
+      <c r="N360" s="2" t="inlineStr">
+        <is>
+          <t>grapecircus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O360" s="2" t="inlineStr"/>
+      <c r="P360" s="2" t="inlineStr"/>
+      <c r="Q360" s="2" t="inlineStr"/>
+      <c r="R360" s="2" t="inlineStr"/>
+      <c r="S360" s="2" t="inlineStr"/>
+      <c r="T360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grapecircus</t>
+        </is>
+      </c>
+      <c r="U360" s="2" t="inlineStr"/>
+      <c r="V360" s="2" t="inlineStr"/>
+      <c r="W360" s="2" t="inlineStr">
+        <is>
+          <t>Philippa Moore</t>
+        </is>
+      </c>
+      <c r="X360" s="2" t="inlineStr">
+        <is>
+          <t>In Charge</t>
+        </is>
+      </c>
+      <c r="Y360" s="2" t="inlineStr"/>
+      <c r="Z360" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA360" s="2" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>Enowine</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>Enowine</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>Co. Meath</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>Unit 14, East Mullaghboy Industrial Estate</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>C15 C603</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>https://enowine.ie</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr"/>
+      <c r="K361" s="2" t="inlineStr"/>
+      <c r="L361" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="inlineStr"/>
+      <c r="N361" s="2" t="inlineStr">
+        <is>
+          <t>info@enowine.ie</t>
+        </is>
+      </c>
+      <c r="O361" s="2" t="inlineStr">
+        <is>
+          <t>+353 46 907 3613</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="Q361" s="2" t="inlineStr">
+        <is>
+          <t>8526</t>
+        </is>
+      </c>
+      <c r="R361" s="2" t="inlineStr"/>
+      <c r="S361" s="2" t="inlineStr"/>
+      <c r="T361" s="2" t="inlineStr"/>
+      <c r="U361" s="2" t="inlineStr"/>
+      <c r="V361" s="2" t="inlineStr"/>
+      <c r="W361" s="2" t="inlineStr">
+        <is>
+          <t>Damien Brennan</t>
+        </is>
+      </c>
+      <c r="X361" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y361" s="2" t="inlineStr"/>
+      <c r="Z361" s="2" t="inlineStr"/>
+      <c r="AA361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/damien-brennan-007825135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>28883</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 8</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>32 Cook Street</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>D14 F765</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>https://retrovino.com</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr"/>
+      <c r="K362" s="2" t="inlineStr"/>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="inlineStr"/>
+      <c r="N362" s="2" t="inlineStr">
+        <is>
+          <t>info@retrovino.com</t>
+        </is>
+      </c>
+      <c r="O362" s="2" t="inlineStr"/>
+      <c r="P362" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q362" s="2" t="inlineStr"/>
+      <c r="R362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/retrovino.com/</t>
+        </is>
+      </c>
+      <c r="S362" s="2" t="inlineStr"/>
+      <c r="T362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/retrovino_sake</t>
+        </is>
+      </c>
+      <c r="U362" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/retrovino</t>
+        </is>
+      </c>
+      <c r="V362" s="2" t="inlineStr"/>
+      <c r="W362" s="2" t="inlineStr">
+        <is>
+          <t>Colly Murray</t>
+        </is>
+      </c>
+      <c r="X362" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y362" s="2" t="inlineStr"/>
+      <c r="Z362" s="2" t="inlineStr"/>
+      <c r="AA362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/collymurray/</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr"/>
+      <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr"/>
+      <c r="M363" s="2" t="inlineStr"/>
+      <c r="N363" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O363" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P363" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U363" s="2" t="inlineStr"/>
+      <c r="V363" s="2" t="inlineStr"/>
+      <c r="W363" s="2" t="inlineStr">
+        <is>
+          <t>Oana Cristina</t>
+        </is>
+      </c>
+      <c r="X363" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Officer</t>
+        </is>
+      </c>
+      <c r="Y363" s="2" t="inlineStr"/>
+      <c r="Z363" s="2" t="inlineStr"/>
+      <c r="AA363" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/stamatinoana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr"/>
+      <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr"/>
+      <c r="M364" s="2" t="inlineStr"/>
+      <c r="N364" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O364" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U364" s="2" t="inlineStr"/>
+      <c r="V364" s="2" t="inlineStr"/>
+      <c r="W364" s="2" t="inlineStr">
+        <is>
+          <t>Sergey Ternovskiy</t>
+        </is>
+      </c>
+      <c r="X364" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y364" s="2" t="inlineStr"/>
+      <c r="Z364" s="2" t="inlineStr"/>
+      <c r="AA364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sergey-ternovskiy-53763752/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr"/>
+      <c r="K365" s="2" t="inlineStr"/>
+      <c r="L365" s="2" t="inlineStr"/>
+      <c r="M365" s="2" t="inlineStr"/>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U365" s="2" t="inlineStr"/>
+      <c r="V365" s="2" t="inlineStr"/>
+      <c r="W365" s="2" t="inlineStr">
+        <is>
+          <t>Alexandr Gazibar</t>
+        </is>
+      </c>
+      <c r="X365" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y365" s="2" t="inlineStr"/>
+      <c r="Z365" s="2" t="inlineStr"/>
+      <c r="AA365" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/alexandr-gazibar-8a424821a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>29607</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 3</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>48 Clontarf Road, Clontarf</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>D03 RR40</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clontarfwines.ie</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr"/>
+      <c r="K366" s="2" t="inlineStr"/>
+      <c r="L366" s="2" t="inlineStr"/>
+      <c r="M366" s="2" t="inlineStr"/>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>clontarfwines@gmail.com</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 853 3088</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="inlineStr"/>
+      <c r="Q366" s="2" t="inlineStr"/>
+      <c r="R366" s="2" t="inlineStr"/>
+      <c r="S366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/clontarf-wines-296283393843216/</t>
+        </is>
+      </c>
+      <c r="T366" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/clontarfwines</t>
+        </is>
+      </c>
+      <c r="U366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="inlineStr"/>
+      <c r="W366" s="2" t="inlineStr">
+        <is>
+          <t>Ronnie Caraher</t>
+        </is>
+      </c>
+      <c r="X366" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y366" s="2" t="inlineStr"/>
+      <c r="Z366" s="2" t="inlineStr"/>
+      <c r="AA366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronnie-caraher-7b36ab113/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr"/>
+      <c r="K367" s="2" t="inlineStr"/>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr"/>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O367" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="inlineStr"/>
+      <c r="S367" s="2" t="inlineStr"/>
+      <c r="T367" s="2" t="inlineStr"/>
+      <c r="U367" s="2" t="inlineStr"/>
+      <c r="V367" s="2" t="inlineStr"/>
+      <c r="W367" s="2" t="inlineStr">
+        <is>
+          <t>William Doogan</t>
+        </is>
+      </c>
+      <c r="X367" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y367" s="2" t="inlineStr"/>
+      <c r="Z367" s="2" t="inlineStr"/>
+      <c r="AA367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-doogan-00b52540/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr"/>
+      <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr"/>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="inlineStr"/>
+      <c r="S368" s="2" t="inlineStr"/>
+      <c r="T368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="inlineStr"/>
+      <c r="V368" s="2" t="inlineStr"/>
+      <c r="W368" s="2" t="inlineStr">
+        <is>
+          <t>Paul Flynn</t>
+        </is>
+      </c>
+      <c r="X368" s="2" t="inlineStr">
+        <is>
+          <t>Sales Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y368" s="2" t="inlineStr"/>
+      <c r="Z368" s="2" t="inlineStr"/>
+      <c r="AA368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulflynnthewineguyni/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>54646</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Tralee</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>County Kerry</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>80 Boherbee, Cloonalour</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>V92 TW90</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>https://nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr"/>
+      <c r="K369" s="2" t="inlineStr"/>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr"/>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>info@nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t>+353 66 718 0360</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>65599</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/castle-off-licence/</t>
+        </is>
+      </c>
+      <c r="S369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/castleofflicence</t>
+        </is>
+      </c>
+      <c r="T369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/castle.offy.tralee/</t>
+        </is>
+      </c>
+      <c r="U369" s="2" t="inlineStr"/>
+      <c r="V369" s="2" t="inlineStr"/>
+      <c r="W369" s="2" t="inlineStr">
+        <is>
+          <t>Fiona Palfrey</t>
+        </is>
+      </c>
+      <c r="X369" s="2" t="inlineStr">
+        <is>
+          <t>General Manager/ Director</t>
+        </is>
+      </c>
+      <c r="Y369" s="2" t="inlineStr"/>
+      <c r="Z369" s="2" t="inlineStr"/>
+      <c r="AA369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fiona-palfrey-46825722</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>8060</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Galway</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>County Galway</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>3 Middle Street Mews, Middle Street</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>H91 C2V4</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr"/>
+      <c r="K370" s="2" t="inlineStr"/>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr"/>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>info@woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr">
+        <is>
+          <t>+353 91 533 706</t>
+        </is>
+      </c>
+      <c r="P370" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="Q370" s="2" t="inlineStr"/>
+      <c r="R370" s="2" t="inlineStr"/>
+      <c r="S370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/woodberrys</t>
+        </is>
+      </c>
+      <c r="T370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woodberrywines/</t>
+        </is>
+      </c>
+      <c r="U370" s="2" t="inlineStr"/>
+      <c r="V370" s="2" t="inlineStr"/>
+      <c r="W370" s="2" t="inlineStr"/>
+      <c r="X370" s="2" t="inlineStr"/>
+      <c r="Y370" s="2" t="inlineStr"/>
+      <c r="Z370" s="2" t="inlineStr"/>
+      <c r="AA370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr"/>
+      <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr"/>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr"/>
+      <c r="P371" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R371" s="2" t="inlineStr"/>
+      <c r="S371" s="2" t="inlineStr"/>
+      <c r="T371" s="2" t="inlineStr"/>
+      <c r="U371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="inlineStr"/>
+      <c r="W371" s="2" t="inlineStr">
+        <is>
+          <t>John Donohoe</t>
+        </is>
+      </c>
+      <c r="X371" s="2" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="Y371" s="2" t="inlineStr"/>
+      <c r="Z371" s="2" t="inlineStr"/>
+      <c r="AA371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-donohoe-48a5a33b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr"/>
+      <c r="K372" s="2" t="inlineStr"/>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="inlineStr"/>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr"/>
+      <c r="P372" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R372" s="2" t="inlineStr"/>
+      <c r="S372" s="2" t="inlineStr"/>
+      <c r="T372" s="2" t="inlineStr"/>
+      <c r="U372" s="2" t="inlineStr"/>
+      <c r="V372" s="2" t="inlineStr"/>
+      <c r="W372" s="2" t="inlineStr">
+        <is>
+          <t>James O’hara</t>
+        </is>
+      </c>
+      <c r="X372" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y372" s="2" t="inlineStr"/>
+      <c r="Z372" s="2" t="inlineStr"/>
+      <c r="AA372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-o-hara-45a93138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr"/>
+      <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr"/>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O373" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P373" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="inlineStr"/>
+      <c r="W373" s="2" t="inlineStr">
+        <is>
+          <t>Marilia Carraro</t>
+        </is>
+      </c>
+      <c r="X373" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y373" s="2" t="inlineStr"/>
+      <c r="Z373" s="2" t="inlineStr"/>
+      <c r="AA373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mariliacarraro/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr"/>
+      <c r="K374" s="2" t="inlineStr"/>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr"/>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P374" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="inlineStr"/>
+      <c r="W374" s="2" t="inlineStr">
+        <is>
+          <t>Piero Murgia</t>
+        </is>
+      </c>
+      <c r="X374" s="2" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y374" s="2" t="inlineStr"/>
+      <c r="Z374" s="2" t="inlineStr"/>
+      <c r="AA374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/piero-murgia-313003150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr"/>
+      <c r="K375" s="2" t="inlineStr"/>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr"/>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P375" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="inlineStr"/>
+      <c r="W375" s="2" t="inlineStr">
+        <is>
+          <t>Daragh Monahan</t>
+        </is>
+      </c>
+      <c r="X375" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Sales</t>
+        </is>
+      </c>
+      <c r="Y375" s="2" t="inlineStr"/>
+      <c r="Z375" s="2" t="inlineStr"/>
+      <c r="AA375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daragh-monahan-4716881a3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr"/>
+      <c r="K376" s="2" t="inlineStr"/>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr"/>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P376" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q376" s="2" t="inlineStr"/>
+      <c r="R376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U376" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V376" s="2" t="inlineStr"/>
+      <c r="W376" s="2" t="inlineStr">
+        <is>
+          <t>Avril Kirrane</t>
+        </is>
+      </c>
+      <c r="X376" s="2" t="inlineStr">
+        <is>
+          <t>Wine Specialist &amp; Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y376" s="2" t="inlineStr"/>
+      <c r="Z376" s="2" t="inlineStr"/>
+      <c r="AA376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avril-kirrane-42055115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr"/>
+      <c r="K377" s="2" t="inlineStr"/>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr"/>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O377" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P377" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q377" s="2" t="inlineStr"/>
+      <c r="R377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U377" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V377" s="2" t="inlineStr"/>
+      <c r="W377" s="2" t="inlineStr">
+        <is>
+          <t>Johnny Mcmorrough</t>
+        </is>
+      </c>
+      <c r="X377" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y377" s="2" t="inlineStr"/>
+      <c r="Z377" s="2" t="inlineStr"/>
+      <c r="AA377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johnny-mcmorrough-32597a3a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>Kilkenny</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Co. Kilkenny</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>Market Yard</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>R95 FH05</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>https://lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr"/>
+      <c r="K378" s="2" t="inlineStr"/>
+      <c r="L378" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="inlineStr"/>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>orders@lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="O378" s="2" t="inlineStr">
+        <is>
+          <t>+353 56 775 2166</t>
+        </is>
+      </c>
+      <c r="P378" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q378" s="2" t="inlineStr">
+        <is>
+          <t>311736</t>
+        </is>
+      </c>
+      <c r="R378" s="2" t="inlineStr"/>
+      <c r="S378" s="2" t="inlineStr"/>
+      <c r="T378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lecaveauwinemerchants</t>
+        </is>
+      </c>
+      <c r="U378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="inlineStr"/>
+      <c r="W378" s="2" t="inlineStr">
+        <is>
+          <t>Pascal Rossignol</t>
+        </is>
+      </c>
+      <c r="X378" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Owner</t>
+        </is>
+      </c>
+      <c r="Y378" s="2" t="inlineStr"/>
+      <c r="Z378" s="2" t="inlineStr"/>
+      <c r="AA378" s="2" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>23827</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>Co. Louth</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>Williamson's Mall, Francis Street, Townparks</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>A91 NR29</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr"/>
+      <c r="K379" s="2" t="inlineStr"/>
+      <c r="L379" s="2" t="inlineStr"/>
+      <c r="M379" s="2" t="inlineStr"/>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>info@dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="O379" s="2" t="inlineStr"/>
+      <c r="P379" s="2" t="inlineStr"/>
+      <c r="Q379" s="2" t="inlineStr"/>
+      <c r="R379" s="2" t="inlineStr"/>
+      <c r="S379" s="2" t="inlineStr"/>
+      <c r="T379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/macguinnesswine/</t>
+        </is>
+      </c>
+      <c r="U379" s="2" t="inlineStr"/>
+      <c r="V379" s="2" t="inlineStr"/>
+      <c r="W379" s="2" t="inlineStr">
+        <is>
+          <t>Alan Mac Guinness Rockwines</t>
+        </is>
+      </c>
+      <c r="X379" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y379" s="2" t="inlineStr"/>
+      <c r="Z379" s="2" t="inlineStr"/>
+      <c r="AA379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alan-mac-guinness-rockwines-69839624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>42229</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>117 Philipsburgh Avenue, Fairview</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>D03 XV04</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>https://sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr"/>
+      <c r="K380" s="2" t="inlineStr"/>
+      <c r="L380" s="2" t="inlineStr"/>
+      <c r="M380" s="2" t="inlineStr"/>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>info@sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="O380" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 837 2857</t>
+        </is>
+      </c>
+      <c r="P380" s="2" t="inlineStr"/>
+      <c r="Q380" s="2" t="inlineStr"/>
+      <c r="R380" s="2" t="inlineStr"/>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Sweeneysd3/</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="U380" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="V380" s="2" t="inlineStr"/>
+      <c r="W380" s="2" t="inlineStr"/>
+      <c r="X380" s="2" t="inlineStr"/>
+      <c r="Y380" s="2" t="inlineStr"/>
+      <c r="Z380" s="2" t="inlineStr"/>
+      <c r="AA380" s="2" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>46310</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>Carry Out Tyrellstown, Unit 7 The Plaza, Tyrellstown Town Centre, Tyrrelstown</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>D15 XF21</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecru.ie</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr"/>
+      <c r="K381" s="2" t="inlineStr"/>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr"/>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>Orders@TheCru.ie</t>
+        </is>
+      </c>
+      <c r="O381" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 485 3171</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q381" s="2" t="inlineStr"/>
+      <c r="R381" s="2" t="inlineStr"/>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com//thecru.ie</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thecru.ie</t>
+        </is>
+      </c>
+      <c r="U381" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCru_IE</t>
+        </is>
+      </c>
+      <c r="V381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCNRk_PWRb3yOQK77FxGVe6g/featured</t>
+        </is>
+      </c>
+      <c r="W381" s="2" t="inlineStr"/>
+      <c r="X381" s="2" t="inlineStr"/>
+      <c r="Y381" s="2" t="inlineStr"/>
+      <c r="Z381" s="2" t="inlineStr"/>
+      <c r="AA381" s="2" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>21158</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>25 Ranelagh, Ranelagh</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>D06 RP40</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.redmonds.ie</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr"/>
+      <c r="K382" s="2" t="inlineStr"/>
+      <c r="L382" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="inlineStr"/>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>info@redmonds.ie</t>
+        </is>
+      </c>
+      <c r="O382" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 496 0552</t>
+        </is>
+      </c>
+      <c r="P382" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q382" s="2" t="inlineStr">
+        <is>
+          <t>51847</t>
+        </is>
+      </c>
+      <c r="R382" s="2" t="inlineStr"/>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/redmonds-off-licence-ranelagh-120637134043/</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr">
+        <is>
+          <t>http://instagram.com/redmondsd6</t>
+        </is>
+      </c>
+      <c r="U382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="inlineStr"/>
+      <c r="W382" s="2" t="inlineStr"/>
+      <c r="X382" s="2" t="inlineStr"/>
+      <c r="Y382" s="2" t="inlineStr"/>
+      <c r="Z382" s="2" t="inlineStr"/>
+      <c r="AA382" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA382"/>
+  <dimension ref="A1:AA410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -42292,6 +42292,2750 @@
       <c r="Z382" s="2" t="inlineStr"/>
       <c r="AA382" s="2" t="inlineStr"/>
     </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr"/>
+      <c r="K383" s="2" t="inlineStr"/>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="inlineStr"/>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O383" s="2" t="inlineStr"/>
+      <c r="P383" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R383" s="2" t="inlineStr"/>
+      <c r="S383" s="2" t="inlineStr"/>
+      <c r="T383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="inlineStr"/>
+      <c r="W383" s="2" t="inlineStr">
+        <is>
+          <t>Jennifer Thompson</t>
+        </is>
+      </c>
+      <c r="X383" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y383" s="2" t="inlineStr"/>
+      <c r="Z383" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA383" s="2" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr"/>
+      <c r="K384" s="2" t="inlineStr"/>
+      <c r="L384" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O384" s="2" t="inlineStr"/>
+      <c r="P384" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q384" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R384" s="2" t="inlineStr"/>
+      <c r="S384" s="2" t="inlineStr"/>
+      <c r="T384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U384" s="2" t="inlineStr"/>
+      <c r="V384" s="2" t="inlineStr"/>
+      <c r="W384" s="2" t="inlineStr">
+        <is>
+          <t>Luis Solé Garriz</t>
+        </is>
+      </c>
+      <c r="X384" s="2" t="inlineStr">
+        <is>
+          <t>Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y384" s="2" t="inlineStr"/>
+      <c r="Z384" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-sole-garriz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr"/>
+      <c r="K385" s="2" t="inlineStr"/>
+      <c r="L385" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="inlineStr"/>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O385" s="2" t="inlineStr"/>
+      <c r="P385" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R385" s="2" t="inlineStr"/>
+      <c r="S385" s="2" t="inlineStr"/>
+      <c r="T385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U385" s="2" t="inlineStr"/>
+      <c r="V385" s="2" t="inlineStr"/>
+      <c r="W385" s="2" t="inlineStr">
+        <is>
+          <t>Anne Rodgers</t>
+        </is>
+      </c>
+      <c r="X385" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y385" s="2" t="inlineStr"/>
+      <c r="Z385" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA385" s="2" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Green Man Wines</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Green Man Wines</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>48604</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 6W</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>3 Terenure Road North</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>D6W PY04</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greenmanwines.ie</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr"/>
+      <c r="K386" s="2" t="inlineStr"/>
+      <c r="L386" s="2" t="inlineStr"/>
+      <c r="M386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr">
+        <is>
+          <t>info@greenmanwines.ie</t>
+        </is>
+      </c>
+      <c r="O386" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 559 4234</t>
+        </is>
+      </c>
+      <c r="P386" s="2" t="inlineStr"/>
+      <c r="Q386" s="2" t="inlineStr"/>
+      <c r="R386" s="2" t="inlineStr"/>
+      <c r="S386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GreenManWines</t>
+        </is>
+      </c>
+      <c r="T386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/green_man_wines</t>
+        </is>
+      </c>
+      <c r="U386" s="2" t="inlineStr"/>
+      <c r="V386" s="2" t="inlineStr"/>
+      <c r="W386" s="2" t="inlineStr">
+        <is>
+          <t>David Gallagher</t>
+        </is>
+      </c>
+      <c r="X386" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Director</t>
+        </is>
+      </c>
+      <c r="Y386" s="2" t="inlineStr"/>
+      <c r="Z386" s="2" t="inlineStr"/>
+      <c r="AA386" s="2" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>39954</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>26 Pembroke Street Upper</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>D02 X361</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>https://grapecircus.ie, https://www.grapecircus.com</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr"/>
+      <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr"/>
+      <c r="M387" s="2" t="inlineStr"/>
+      <c r="N387" s="2" t="inlineStr">
+        <is>
+          <t>grapecircus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O387" s="2" t="inlineStr"/>
+      <c r="P387" s="2" t="inlineStr"/>
+      <c r="Q387" s="2" t="inlineStr"/>
+      <c r="R387" s="2" t="inlineStr"/>
+      <c r="S387" s="2" t="inlineStr"/>
+      <c r="T387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grapecircus</t>
+        </is>
+      </c>
+      <c r="U387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr"/>
+      <c r="W387" s="2" t="inlineStr">
+        <is>
+          <t>Enrico Fantasia</t>
+        </is>
+      </c>
+      <c r="X387" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y387" s="2" t="inlineStr"/>
+      <c r="Z387" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/enrico-fantasia-247b4838/</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>39954</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>26 Pembroke Street Upper</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>D02 X361</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>https://grapecircus.ie, https://www.grapecircus.com</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr"/>
+      <c r="K388" s="2" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr"/>
+      <c r="M388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr">
+        <is>
+          <t>grapecircus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O388" s="2" t="inlineStr"/>
+      <c r="P388" s="2" t="inlineStr"/>
+      <c r="Q388" s="2" t="inlineStr"/>
+      <c r="R388" s="2" t="inlineStr"/>
+      <c r="S388" s="2" t="inlineStr"/>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grapecircus</t>
+        </is>
+      </c>
+      <c r="U388" s="2" t="inlineStr"/>
+      <c r="V388" s="2" t="inlineStr"/>
+      <c r="W388" s="2" t="inlineStr">
+        <is>
+          <t>Philippa Moore</t>
+        </is>
+      </c>
+      <c r="X388" s="2" t="inlineStr">
+        <is>
+          <t>In Charge</t>
+        </is>
+      </c>
+      <c r="Y388" s="2" t="inlineStr"/>
+      <c r="Z388" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA388" s="2" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Enowine</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>Enowine</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>Co. Meath</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>Unit 14, East Mullaghboy Industrial Estate</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>C15 C603</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>https://enowine.ie</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr"/>
+      <c r="K389" s="2" t="inlineStr"/>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="inlineStr"/>
+      <c r="N389" s="2" t="inlineStr">
+        <is>
+          <t>info@enowine.ie</t>
+        </is>
+      </c>
+      <c r="O389" s="2" t="inlineStr">
+        <is>
+          <t>+353 46 907 3613</t>
+        </is>
+      </c>
+      <c r="P389" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>8526</t>
+        </is>
+      </c>
+      <c r="R389" s="2" t="inlineStr"/>
+      <c r="S389" s="2" t="inlineStr"/>
+      <c r="T389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="inlineStr"/>
+      <c r="V389" s="2" t="inlineStr"/>
+      <c r="W389" s="2" t="inlineStr">
+        <is>
+          <t>Damien Brennan</t>
+        </is>
+      </c>
+      <c r="X389" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y389" s="2" t="inlineStr"/>
+      <c r="Z389" s="2" t="inlineStr"/>
+      <c r="AA389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/damien-brennan-007825135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>28883</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 8</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>32 Cook Street</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>D14 F765</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>https://retrovino.com</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr"/>
+      <c r="K390" s="2" t="inlineStr"/>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr">
+        <is>
+          <t>info@retrovino.com</t>
+        </is>
+      </c>
+      <c r="O390" s="2" t="inlineStr"/>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q390" s="2" t="inlineStr"/>
+      <c r="R390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/retrovino.com/</t>
+        </is>
+      </c>
+      <c r="S390" s="2" t="inlineStr"/>
+      <c r="T390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/retrovino_sake</t>
+        </is>
+      </c>
+      <c r="U390" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/retrovino</t>
+        </is>
+      </c>
+      <c r="V390" s="2" t="inlineStr"/>
+      <c r="W390" s="2" t="inlineStr">
+        <is>
+          <t>Colly Murray</t>
+        </is>
+      </c>
+      <c r="X390" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y390" s="2" t="inlineStr"/>
+      <c r="Z390" s="2" t="inlineStr"/>
+      <c r="AA390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/collymurray/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr"/>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr"/>
+      <c r="M391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O391" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U391" s="2" t="inlineStr"/>
+      <c r="V391" s="2" t="inlineStr"/>
+      <c r="W391" s="2" t="inlineStr">
+        <is>
+          <t>Oana Cristina</t>
+        </is>
+      </c>
+      <c r="X391" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Officer</t>
+        </is>
+      </c>
+      <c r="Y391" s="2" t="inlineStr"/>
+      <c r="Z391" s="2" t="inlineStr"/>
+      <c r="AA391" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/stamatinoana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr"/>
+      <c r="K392" s="2" t="inlineStr"/>
+      <c r="L392" s="2" t="inlineStr"/>
+      <c r="M392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O392" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P392" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="inlineStr"/>
+      <c r="W392" s="2" t="inlineStr">
+        <is>
+          <t>Sergey Ternovskiy</t>
+        </is>
+      </c>
+      <c r="X392" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y392" s="2" t="inlineStr"/>
+      <c r="Z392" s="2" t="inlineStr"/>
+      <c r="AA392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sergey-ternovskiy-53763752/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr"/>
+      <c r="K393" s="2" t="inlineStr"/>
+      <c r="L393" s="2" t="inlineStr"/>
+      <c r="M393" s="2" t="inlineStr"/>
+      <c r="N393" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O393" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="inlineStr"/>
+      <c r="W393" s="2" t="inlineStr">
+        <is>
+          <t>Alexandr Gazibar</t>
+        </is>
+      </c>
+      <c r="X393" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y393" s="2" t="inlineStr"/>
+      <c r="Z393" s="2" t="inlineStr"/>
+      <c r="AA393" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/alexandr-gazibar-8a424821a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>29607</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 3</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>48 Clontarf Road, Clontarf</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>D03 RR40</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clontarfwines.ie</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr"/>
+      <c r="K394" s="2" t="inlineStr"/>
+      <c r="L394" s="2" t="inlineStr"/>
+      <c r="M394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr">
+        <is>
+          <t>clontarfwines@gmail.com</t>
+        </is>
+      </c>
+      <c r="O394" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 853 3088</t>
+        </is>
+      </c>
+      <c r="P394" s="2" t="inlineStr"/>
+      <c r="Q394" s="2" t="inlineStr"/>
+      <c r="R394" s="2" t="inlineStr"/>
+      <c r="S394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/clontarf-wines-296283393843216/</t>
+        </is>
+      </c>
+      <c r="T394" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/clontarfwines</t>
+        </is>
+      </c>
+      <c r="U394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="inlineStr"/>
+      <c r="W394" s="2" t="inlineStr">
+        <is>
+          <t>Ronnie Caraher</t>
+        </is>
+      </c>
+      <c r="X394" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y394" s="2" t="inlineStr"/>
+      <c r="Z394" s="2" t="inlineStr"/>
+      <c r="AA394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronnie-caraher-7b36ab113/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr"/>
+      <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="inlineStr"/>
+      <c r="N395" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O395" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P395" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R395" s="2" t="inlineStr"/>
+      <c r="S395" s="2" t="inlineStr"/>
+      <c r="T395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="inlineStr"/>
+      <c r="V395" s="2" t="inlineStr"/>
+      <c r="W395" s="2" t="inlineStr">
+        <is>
+          <t>William Doogan</t>
+        </is>
+      </c>
+      <c r="X395" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y395" s="2" t="inlineStr"/>
+      <c r="Z395" s="2" t="inlineStr"/>
+      <c r="AA395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-doogan-00b52540/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr"/>
+      <c r="K396" s="2" t="inlineStr"/>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="inlineStr"/>
+      <c r="N396" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O396" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P396" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q396" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R396" s="2" t="inlineStr"/>
+      <c r="S396" s="2" t="inlineStr"/>
+      <c r="T396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="inlineStr"/>
+      <c r="V396" s="2" t="inlineStr"/>
+      <c r="W396" s="2" t="inlineStr">
+        <is>
+          <t>Paul Flynn</t>
+        </is>
+      </c>
+      <c r="X396" s="2" t="inlineStr">
+        <is>
+          <t>Sales Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y396" s="2" t="inlineStr"/>
+      <c r="Z396" s="2" t="inlineStr"/>
+      <c r="AA396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulflynnthewineguyni/</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>54646</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>Tralee</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>County Kerry</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>80 Boherbee, Cloonalour</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>V92 TW90</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>https://nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr"/>
+      <c r="K397" s="2" t="inlineStr"/>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="inlineStr"/>
+      <c r="N397" s="2" t="inlineStr">
+        <is>
+          <t>info@nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="O397" s="2" t="inlineStr">
+        <is>
+          <t>+353 66 718 0360</t>
+        </is>
+      </c>
+      <c r="P397" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>65599</t>
+        </is>
+      </c>
+      <c r="R397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/castle-off-licence/</t>
+        </is>
+      </c>
+      <c r="S397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/castleofflicence</t>
+        </is>
+      </c>
+      <c r="T397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/castle.offy.tralee/</t>
+        </is>
+      </c>
+      <c r="U397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="inlineStr"/>
+      <c r="W397" s="2" t="inlineStr">
+        <is>
+          <t>Fiona Palfrey</t>
+        </is>
+      </c>
+      <c r="X397" s="2" t="inlineStr">
+        <is>
+          <t>General Manager/ Director</t>
+        </is>
+      </c>
+      <c r="Y397" s="2" t="inlineStr"/>
+      <c r="Z397" s="2" t="inlineStr"/>
+      <c r="AA397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fiona-palfrey-46825722</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>8060</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>Galway</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>County Galway</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>3 Middle Street Mews, Middle Street</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>H91 C2V4</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr"/>
+      <c r="K398" s="2" t="inlineStr"/>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="inlineStr"/>
+      <c r="N398" s="2" t="inlineStr">
+        <is>
+          <t>info@woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="O398" s="2" t="inlineStr">
+        <is>
+          <t>+353 91 533 706</t>
+        </is>
+      </c>
+      <c r="P398" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="Q398" s="2" t="inlineStr"/>
+      <c r="R398" s="2" t="inlineStr"/>
+      <c r="S398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/woodberrys</t>
+        </is>
+      </c>
+      <c r="T398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woodberrywines/</t>
+        </is>
+      </c>
+      <c r="U398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="inlineStr"/>
+      <c r="W398" s="2" t="inlineStr"/>
+      <c r="X398" s="2" t="inlineStr"/>
+      <c r="Y398" s="2" t="inlineStr"/>
+      <c r="Z398" s="2" t="inlineStr"/>
+      <c r="AA398" s="2" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr"/>
+      <c r="K399" s="2" t="inlineStr"/>
+      <c r="L399" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="inlineStr"/>
+      <c r="N399" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O399" s="2" t="inlineStr"/>
+      <c r="P399" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q399" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R399" s="2" t="inlineStr"/>
+      <c r="S399" s="2" t="inlineStr"/>
+      <c r="T399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="inlineStr"/>
+      <c r="V399" s="2" t="inlineStr"/>
+      <c r="W399" s="2" t="inlineStr">
+        <is>
+          <t>John Donohoe</t>
+        </is>
+      </c>
+      <c r="X399" s="2" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="Y399" s="2" t="inlineStr"/>
+      <c r="Z399" s="2" t="inlineStr"/>
+      <c r="AA399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-donohoe-48a5a33b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr"/>
+      <c r="K400" s="2" t="inlineStr"/>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr"/>
+      <c r="N400" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O400" s="2" t="inlineStr"/>
+      <c r="P400" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R400" s="2" t="inlineStr"/>
+      <c r="S400" s="2" t="inlineStr"/>
+      <c r="T400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="inlineStr"/>
+      <c r="V400" s="2" t="inlineStr"/>
+      <c r="W400" s="2" t="inlineStr">
+        <is>
+          <t>James O’hara</t>
+        </is>
+      </c>
+      <c r="X400" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y400" s="2" t="inlineStr"/>
+      <c r="Z400" s="2" t="inlineStr"/>
+      <c r="AA400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-o-hara-45a93138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr"/>
+      <c r="K401" s="2" t="inlineStr"/>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="inlineStr"/>
+      <c r="N401" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O401" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P401" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="inlineStr"/>
+      <c r="W401" s="2" t="inlineStr">
+        <is>
+          <t>Marilia Carraro</t>
+        </is>
+      </c>
+      <c r="X401" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y401" s="2" t="inlineStr"/>
+      <c r="Z401" s="2" t="inlineStr"/>
+      <c r="AA401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mariliacarraro/</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr"/>
+      <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr"/>
+      <c r="N402" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O402" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P402" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="inlineStr"/>
+      <c r="W402" s="2" t="inlineStr">
+        <is>
+          <t>Piero Murgia</t>
+        </is>
+      </c>
+      <c r="X402" s="2" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y402" s="2" t="inlineStr"/>
+      <c r="Z402" s="2" t="inlineStr"/>
+      <c r="AA402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/piero-murgia-313003150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr"/>
+      <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr"/>
+      <c r="N403" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O403" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P403" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="inlineStr"/>
+      <c r="W403" s="2" t="inlineStr">
+        <is>
+          <t>Daragh Monahan</t>
+        </is>
+      </c>
+      <c r="X403" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Sales</t>
+        </is>
+      </c>
+      <c r="Y403" s="2" t="inlineStr"/>
+      <c r="Z403" s="2" t="inlineStr"/>
+      <c r="AA403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daragh-monahan-4716881a3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr"/>
+      <c r="K404" s="2" t="inlineStr"/>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr"/>
+      <c r="N404" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O404" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P404" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q404" s="2" t="inlineStr"/>
+      <c r="R404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U404" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V404" s="2" t="inlineStr"/>
+      <c r="W404" s="2" t="inlineStr">
+        <is>
+          <t>Avril Kirrane</t>
+        </is>
+      </c>
+      <c r="X404" s="2" t="inlineStr">
+        <is>
+          <t>Wine Specialist &amp; Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y404" s="2" t="inlineStr"/>
+      <c r="Z404" s="2" t="inlineStr"/>
+      <c r="AA404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avril-kirrane-42055115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr"/>
+      <c r="K405" s="2" t="inlineStr"/>
+      <c r="L405" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="inlineStr"/>
+      <c r="N405" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O405" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P405" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q405" s="2" t="inlineStr"/>
+      <c r="R405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U405" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V405" s="2" t="inlineStr"/>
+      <c r="W405" s="2" t="inlineStr">
+        <is>
+          <t>Johnny Mcmorrough</t>
+        </is>
+      </c>
+      <c r="X405" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y405" s="2" t="inlineStr"/>
+      <c r="Z405" s="2" t="inlineStr"/>
+      <c r="AA405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johnny-mcmorrough-32597a3a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>Kilkenny</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>Co. Kilkenny</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>Market Yard</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>R95 FH05</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>https://lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr"/>
+      <c r="K406" s="2" t="inlineStr"/>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="inlineStr"/>
+      <c r="N406" s="2" t="inlineStr">
+        <is>
+          <t>orders@lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="O406" s="2" t="inlineStr">
+        <is>
+          <t>+353 56 775 2166</t>
+        </is>
+      </c>
+      <c r="P406" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q406" s="2" t="inlineStr">
+        <is>
+          <t>311736</t>
+        </is>
+      </c>
+      <c r="R406" s="2" t="inlineStr"/>
+      <c r="S406" s="2" t="inlineStr"/>
+      <c r="T406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lecaveauwinemerchants</t>
+        </is>
+      </c>
+      <c r="U406" s="2" t="inlineStr"/>
+      <c r="V406" s="2" t="inlineStr"/>
+      <c r="W406" s="2" t="inlineStr">
+        <is>
+          <t>Pascal Rossignol</t>
+        </is>
+      </c>
+      <c r="X406" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Owner</t>
+        </is>
+      </c>
+      <c r="Y406" s="2" t="inlineStr"/>
+      <c r="Z406" s="2" t="inlineStr"/>
+      <c r="AA406" s="2" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>23827</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>Co. Louth</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>Williamson's Mall, Francis Street, Townparks</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>A91 NR29</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr"/>
+      <c r="K407" s="2" t="inlineStr"/>
+      <c r="L407" s="2" t="inlineStr"/>
+      <c r="M407" s="2" t="inlineStr"/>
+      <c r="N407" s="2" t="inlineStr">
+        <is>
+          <t>info@dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="O407" s="2" t="inlineStr"/>
+      <c r="P407" s="2" t="inlineStr"/>
+      <c r="Q407" s="2" t="inlineStr"/>
+      <c r="R407" s="2" t="inlineStr"/>
+      <c r="S407" s="2" t="inlineStr"/>
+      <c r="T407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/macguinnesswine/</t>
+        </is>
+      </c>
+      <c r="U407" s="2" t="inlineStr"/>
+      <c r="V407" s="2" t="inlineStr"/>
+      <c r="W407" s="2" t="inlineStr">
+        <is>
+          <t>Alan Mac Guinness Rockwines</t>
+        </is>
+      </c>
+      <c r="X407" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y407" s="2" t="inlineStr"/>
+      <c r="Z407" s="2" t="inlineStr"/>
+      <c r="AA407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alan-mac-guinness-rockwines-69839624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>42229</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>117 Philipsburgh Avenue, Fairview</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>D03 XV04</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>https://sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr"/>
+      <c r="K408" s="2" t="inlineStr"/>
+      <c r="L408" s="2" t="inlineStr"/>
+      <c r="M408" s="2" t="inlineStr"/>
+      <c r="N408" s="2" t="inlineStr">
+        <is>
+          <t>info@sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="O408" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 837 2857</t>
+        </is>
+      </c>
+      <c r="P408" s="2" t="inlineStr"/>
+      <c r="Q408" s="2" t="inlineStr"/>
+      <c r="R408" s="2" t="inlineStr"/>
+      <c r="S408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Sweeneysd3/</t>
+        </is>
+      </c>
+      <c r="T408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="U408" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="V408" s="2" t="inlineStr"/>
+      <c r="W408" s="2" t="inlineStr"/>
+      <c r="X408" s="2" t="inlineStr"/>
+      <c r="Y408" s="2" t="inlineStr"/>
+      <c r="Z408" s="2" t="inlineStr"/>
+      <c r="AA408" s="2" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>46310</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>Carry Out Tyrellstown, Unit 7 The Plaza, Tyrellstown Town Centre, Tyrrelstown</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>D15 XF21</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecru.ie</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr"/>
+      <c r="K409" s="2" t="inlineStr"/>
+      <c r="L409" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M409" s="2" t="inlineStr"/>
+      <c r="N409" s="2" t="inlineStr">
+        <is>
+          <t>Orders@TheCru.ie</t>
+        </is>
+      </c>
+      <c r="O409" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 485 3171</t>
+        </is>
+      </c>
+      <c r="P409" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q409" s="2" t="inlineStr"/>
+      <c r="R409" s="2" t="inlineStr"/>
+      <c r="S409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com//thecru.ie</t>
+        </is>
+      </c>
+      <c r="T409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thecru.ie</t>
+        </is>
+      </c>
+      <c r="U409" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCru_IE</t>
+        </is>
+      </c>
+      <c r="V409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCNRk_PWRb3yOQK77FxGVe6g/featured</t>
+        </is>
+      </c>
+      <c r="W409" s="2" t="inlineStr"/>
+      <c r="X409" s="2" t="inlineStr"/>
+      <c r="Y409" s="2" t="inlineStr"/>
+      <c r="Z409" s="2" t="inlineStr"/>
+      <c r="AA409" s="2" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>21158</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>25 Ranelagh, Ranelagh</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>D06 RP40</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.redmonds.ie</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr"/>
+      <c r="K410" s="2" t="inlineStr"/>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="inlineStr"/>
+      <c r="N410" s="2" t="inlineStr">
+        <is>
+          <t>info@redmonds.ie</t>
+        </is>
+      </c>
+      <c r="O410" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 496 0552</t>
+        </is>
+      </c>
+      <c r="P410" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>51847</t>
+        </is>
+      </c>
+      <c r="R410" s="2" t="inlineStr"/>
+      <c r="S410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/redmonds-off-licence-ranelagh-120637134043/</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="inlineStr">
+        <is>
+          <t>http://instagram.com/redmondsd6</t>
+        </is>
+      </c>
+      <c r="U410" s="2" t="inlineStr"/>
+      <c r="V410" s="2" t="inlineStr"/>
+      <c r="W410" s="2" t="inlineStr"/>
+      <c r="X410" s="2" t="inlineStr"/>
+      <c r="Y410" s="2" t="inlineStr"/>
+      <c r="Z410" s="2" t="inlineStr"/>
+      <c r="AA410" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ireland.xlsx
+++ b/BWI/bestwine_output/bestwine_Ireland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA410"/>
+  <dimension ref="A1:AA438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -45036,6 +45036,2750 @@
       <c r="Z410" s="2" t="inlineStr"/>
       <c r="AA410" s="2" t="inlineStr"/>
     </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr"/>
+      <c r="K411" s="2" t="inlineStr"/>
+      <c r="L411" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="inlineStr"/>
+      <c r="N411" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O411" s="2" t="inlineStr"/>
+      <c r="P411" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q411" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R411" s="2" t="inlineStr"/>
+      <c r="S411" s="2" t="inlineStr"/>
+      <c r="T411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U411" s="2" t="inlineStr"/>
+      <c r="V411" s="2" t="inlineStr"/>
+      <c r="W411" s="2" t="inlineStr">
+        <is>
+          <t>Jennifer Thompson</t>
+        </is>
+      </c>
+      <c r="X411" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y411" s="2" t="inlineStr"/>
+      <c r="Z411" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA411" s="2" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr"/>
+      <c r="K412" s="2" t="inlineStr"/>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr"/>
+      <c r="N412" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O412" s="2" t="inlineStr"/>
+      <c r="P412" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="inlineStr"/>
+      <c r="S412" s="2" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U412" s="2" t="inlineStr"/>
+      <c r="V412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="inlineStr">
+        <is>
+          <t>Luis Solé Garriz</t>
+        </is>
+      </c>
+      <c r="X412" s="2" t="inlineStr">
+        <is>
+          <t>Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y412" s="2" t="inlineStr"/>
+      <c r="Z412" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-sole-garriz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>Oinos Wines Limited</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>Blackrock</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>Hollytree Cottage, Clonkeen Road</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>A94 X582</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr"/>
+      <c r="K413" s="2" t="inlineStr"/>
+      <c r="L413" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="inlineStr"/>
+      <c r="N413" s="2" t="inlineStr">
+        <is>
+          <t>jennifer@oinoswines.ie</t>
+        </is>
+      </c>
+      <c r="O413" s="2" t="inlineStr"/>
+      <c r="P413" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q413" s="2" t="inlineStr">
+        <is>
+          <t>732915</t>
+        </is>
+      </c>
+      <c r="R413" s="2" t="inlineStr"/>
+      <c r="S413" s="2" t="inlineStr"/>
+      <c r="T413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oinoswines/</t>
+        </is>
+      </c>
+      <c r="U413" s="2" t="inlineStr"/>
+      <c r="V413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr">
+        <is>
+          <t>Anne Rodgers</t>
+        </is>
+      </c>
+      <c r="X413" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y413" s="2" t="inlineStr"/>
+      <c r="Z413" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA413" s="2" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>Green Man Wines</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>Green Man Wines</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>48604</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 6W</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>3 Terenure Road North</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>D6W PY04</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greenmanwines.ie</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr"/>
+      <c r="K414" s="2" t="inlineStr"/>
+      <c r="L414" s="2" t="inlineStr"/>
+      <c r="M414" s="2" t="inlineStr"/>
+      <c r="N414" s="2" t="inlineStr">
+        <is>
+          <t>info@greenmanwines.ie</t>
+        </is>
+      </c>
+      <c r="O414" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 559 4234</t>
+        </is>
+      </c>
+      <c r="P414" s="2" t="inlineStr"/>
+      <c r="Q414" s="2" t="inlineStr"/>
+      <c r="R414" s="2" t="inlineStr"/>
+      <c r="S414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GreenManWines</t>
+        </is>
+      </c>
+      <c r="T414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/green_man_wines</t>
+        </is>
+      </c>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr">
+        <is>
+          <t>David Gallagher</t>
+        </is>
+      </c>
+      <c r="X414" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Director</t>
+        </is>
+      </c>
+      <c r="Y414" s="2" t="inlineStr"/>
+      <c r="Z414" s="2" t="inlineStr"/>
+      <c r="AA414" s="2" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>39954</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>26 Pembroke Street Upper</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>D02 X361</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>https://grapecircus.ie, https://www.grapecircus.com</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr"/>
+      <c r="K415" s="2" t="inlineStr"/>
+      <c r="L415" s="2" t="inlineStr"/>
+      <c r="M415" s="2" t="inlineStr"/>
+      <c r="N415" s="2" t="inlineStr">
+        <is>
+          <t>grapecircus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O415" s="2" t="inlineStr"/>
+      <c r="P415" s="2" t="inlineStr"/>
+      <c r="Q415" s="2" t="inlineStr"/>
+      <c r="R415" s="2" t="inlineStr"/>
+      <c r="S415" s="2" t="inlineStr"/>
+      <c r="T415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grapecircus</t>
+        </is>
+      </c>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr">
+        <is>
+          <t>Enrico Fantasia</t>
+        </is>
+      </c>
+      <c r="X415" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y415" s="2" t="inlineStr"/>
+      <c r="Z415" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/enrico-fantasia-247b4838/</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>Grapecircus Wines</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>39954</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>26 Pembroke Street Upper</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>D02 X361</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>https://grapecircus.ie, https://www.grapecircus.com</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr"/>
+      <c r="K416" s="2" t="inlineStr"/>
+      <c r="L416" s="2" t="inlineStr"/>
+      <c r="M416" s="2" t="inlineStr"/>
+      <c r="N416" s="2" t="inlineStr">
+        <is>
+          <t>grapecircus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O416" s="2" t="inlineStr"/>
+      <c r="P416" s="2" t="inlineStr"/>
+      <c r="Q416" s="2" t="inlineStr"/>
+      <c r="R416" s="2" t="inlineStr"/>
+      <c r="S416" s="2" t="inlineStr"/>
+      <c r="T416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grapecircus</t>
+        </is>
+      </c>
+      <c r="U416" s="2" t="inlineStr"/>
+      <c r="V416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr">
+        <is>
+          <t>Philippa Moore</t>
+        </is>
+      </c>
+      <c r="X416" s="2" t="inlineStr">
+        <is>
+          <t>In Charge</t>
+        </is>
+      </c>
+      <c r="Y416" s="2" t="inlineStr"/>
+      <c r="Z416" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA416" s="2" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>Enowine</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>Enowine</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>Co. Meath</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>Unit 14, East Mullaghboy Industrial Estate</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>C15 C603</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>https://enowine.ie</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr"/>
+      <c r="K417" s="2" t="inlineStr"/>
+      <c r="L417" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M417" s="2" t="inlineStr"/>
+      <c r="N417" s="2" t="inlineStr">
+        <is>
+          <t>info@enowine.ie</t>
+        </is>
+      </c>
+      <c r="O417" s="2" t="inlineStr">
+        <is>
+          <t>+353 46 907 3613</t>
+        </is>
+      </c>
+      <c r="P417" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="Q417" s="2" t="inlineStr">
+        <is>
+          <t>8526</t>
+        </is>
+      </c>
+      <c r="R417" s="2" t="inlineStr"/>
+      <c r="S417" s="2" t="inlineStr"/>
+      <c r="T417" s="2" t="inlineStr"/>
+      <c r="U417" s="2" t="inlineStr"/>
+      <c r="V417" s="2" t="inlineStr"/>
+      <c r="W417" s="2" t="inlineStr">
+        <is>
+          <t>Damien Brennan</t>
+        </is>
+      </c>
+      <c r="X417" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y417" s="2" t="inlineStr"/>
+      <c r="Z417" s="2" t="inlineStr"/>
+      <c r="AA417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/damien-brennan-007825135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>Retrovino</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>28883</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 8</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Co. Dublin</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>32 Cook Street</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>D14 F765</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://retrovino.com</t>
+        </is>
+      </c>
+      <c r="J418" s="2" t="inlineStr"/>
+      <c r="K418" s="2" t="inlineStr"/>
+      <c r="L418" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M418" s="2" t="inlineStr"/>
+      <c r="N418" s="2" t="inlineStr">
+        <is>
+          <t>info@retrovino.com</t>
+        </is>
+      </c>
+      <c r="O418" s="2" t="inlineStr"/>
+      <c r="P418" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q418" s="2" t="inlineStr"/>
+      <c r="R418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/retrovino.com/</t>
+        </is>
+      </c>
+      <c r="S418" s="2" t="inlineStr"/>
+      <c r="T418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/retrovino_sake</t>
+        </is>
+      </c>
+      <c r="U418" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/retrovino</t>
+        </is>
+      </c>
+      <c r="V418" s="2" t="inlineStr"/>
+      <c r="W418" s="2" t="inlineStr">
+        <is>
+          <t>Colly Murray</t>
+        </is>
+      </c>
+      <c r="X418" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y418" s="2" t="inlineStr"/>
+      <c r="Z418" s="2" t="inlineStr"/>
+      <c r="AA418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/collymurray/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr"/>
+      <c r="K419" s="2" t="inlineStr"/>
+      <c r="L419" s="2" t="inlineStr"/>
+      <c r="M419" s="2" t="inlineStr"/>
+      <c r="N419" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O419" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P419" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q419" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U419" s="2" t="inlineStr"/>
+      <c r="V419" s="2" t="inlineStr"/>
+      <c r="W419" s="2" t="inlineStr">
+        <is>
+          <t>Oana Cristina</t>
+        </is>
+      </c>
+      <c r="X419" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Officer</t>
+        </is>
+      </c>
+      <c r="Y419" s="2" t="inlineStr"/>
+      <c r="Z419" s="2" t="inlineStr"/>
+      <c r="AA419" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/stamatinoana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr"/>
+      <c r="K420" s="2" t="inlineStr"/>
+      <c r="L420" s="2" t="inlineStr"/>
+      <c r="M420" s="2" t="inlineStr"/>
+      <c r="N420" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O420" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P420" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q420" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U420" s="2" t="inlineStr"/>
+      <c r="V420" s="2" t="inlineStr"/>
+      <c r="W420" s="2" t="inlineStr">
+        <is>
+          <t>Alexandr Gazibar</t>
+        </is>
+      </c>
+      <c r="X420" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y420" s="2" t="inlineStr"/>
+      <c r="Z420" s="2" t="inlineStr"/>
+      <c r="AA420" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/alexandr-gazibar-8a424821a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>Tempside Limited</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>Clondalkin</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>Cloverhill Industrial Estate,  , Ballymanaggin</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y767</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polonez.ie</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr"/>
+      <c r="K421" s="2" t="inlineStr"/>
+      <c r="L421" s="2" t="inlineStr"/>
+      <c r="M421" s="2" t="inlineStr"/>
+      <c r="N421" s="2" t="inlineStr">
+        <is>
+          <t>info@polonez.ie</t>
+        </is>
+      </c>
+      <c r="O421" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 457 6888</t>
+        </is>
+      </c>
+      <c r="P421" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q421" s="2" t="inlineStr">
+        <is>
+          <t>474342</t>
+        </is>
+      </c>
+      <c r="R421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/polonezireland/</t>
+        </is>
+      </c>
+      <c r="S421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polonez.ireland</t>
+        </is>
+      </c>
+      <c r="T421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/polonez.ireland/</t>
+        </is>
+      </c>
+      <c r="U421" s="2" t="inlineStr"/>
+      <c r="V421" s="2" t="inlineStr"/>
+      <c r="W421" s="2" t="inlineStr">
+        <is>
+          <t>Sergey Ternovskiy</t>
+        </is>
+      </c>
+      <c r="X421" s="2" t="inlineStr">
+        <is>
+          <t>B2b Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y421" s="2" t="inlineStr"/>
+      <c r="Z421" s="2" t="inlineStr"/>
+      <c r="AA421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sergey-ternovskiy-53763752/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>Clontarf Wines</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>29607</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 3</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>48 Clontarf Road, Clontarf</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>D03 RR40</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clontarfwines.ie</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr"/>
+      <c r="K422" s="2" t="inlineStr"/>
+      <c r="L422" s="2" t="inlineStr"/>
+      <c r="M422" s="2" t="inlineStr"/>
+      <c r="N422" s="2" t="inlineStr">
+        <is>
+          <t>clontarfwines@gmail.com</t>
+        </is>
+      </c>
+      <c r="O422" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 853 3088</t>
+        </is>
+      </c>
+      <c r="P422" s="2" t="inlineStr"/>
+      <c r="Q422" s="2" t="inlineStr"/>
+      <c r="R422" s="2" t="inlineStr"/>
+      <c r="S422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/clontarf-wines-296283393843216/</t>
+        </is>
+      </c>
+      <c r="T422" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/clontarfwines</t>
+        </is>
+      </c>
+      <c r="U422" s="2" t="inlineStr"/>
+      <c r="V422" s="2" t="inlineStr"/>
+      <c r="W422" s="2" t="inlineStr">
+        <is>
+          <t>Ronnie Caraher</t>
+        </is>
+      </c>
+      <c r="X422" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y422" s="2" t="inlineStr"/>
+      <c r="Z422" s="2" t="inlineStr"/>
+      <c r="AA422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronnie-caraher-7b36ab113/?originalSubdomain=ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr"/>
+      <c r="K423" s="2" t="inlineStr"/>
+      <c r="L423" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="inlineStr"/>
+      <c r="N423" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O423" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P423" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q423" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R423" s="2" t="inlineStr"/>
+      <c r="S423" s="2" t="inlineStr"/>
+      <c r="T423" s="2" t="inlineStr"/>
+      <c r="U423" s="2" t="inlineStr"/>
+      <c r="V423" s="2" t="inlineStr"/>
+      <c r="W423" s="2" t="inlineStr">
+        <is>
+          <t>William Doogan</t>
+        </is>
+      </c>
+      <c r="X423" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y423" s="2" t="inlineStr"/>
+      <c r="Z423" s="2" t="inlineStr"/>
+      <c r="AA423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-doogan-00b52540/</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>Mcm Spirits &amp; Liqueurs Limited</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>54645</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>Ballyshannon</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Co. Donegal</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1, Erneside Business Park, Portnason</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>F94 A268</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>https://mcmbrands.ie</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr"/>
+      <c r="K424" s="2" t="inlineStr"/>
+      <c r="L424" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="inlineStr"/>
+      <c r="N424" s="2" t="inlineStr">
+        <is>
+          <t>info@mcmspirits.com</t>
+        </is>
+      </c>
+      <c r="O424" s="2" t="inlineStr">
+        <is>
+          <t>+353 71 985 2434</t>
+        </is>
+      </c>
+      <c r="P424" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q424" s="2" t="inlineStr">
+        <is>
+          <t>376815</t>
+        </is>
+      </c>
+      <c r="R424" s="2" t="inlineStr"/>
+      <c r="S424" s="2" t="inlineStr"/>
+      <c r="T424" s="2" t="inlineStr"/>
+      <c r="U424" s="2" t="inlineStr"/>
+      <c r="V424" s="2" t="inlineStr"/>
+      <c r="W424" s="2" t="inlineStr">
+        <is>
+          <t>Paul Flynn</t>
+        </is>
+      </c>
+      <c r="X424" s="2" t="inlineStr">
+        <is>
+          <t>Sales Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y424" s="2" t="inlineStr"/>
+      <c r="Z424" s="2" t="inlineStr"/>
+      <c r="AA424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulflynnthewineguyni/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>Castle St. Off-licence Company Limited</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>54646</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>Tralee</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>County Kerry</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>80 Boherbee, Cloonalour</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>V92 TW90</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>https://nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr"/>
+      <c r="K425" s="2" t="inlineStr"/>
+      <c r="L425" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="inlineStr"/>
+      <c r="N425" s="2" t="inlineStr">
+        <is>
+          <t>info@nutsaboutwine.ie</t>
+        </is>
+      </c>
+      <c r="O425" s="2" t="inlineStr">
+        <is>
+          <t>+353 66 718 0360</t>
+        </is>
+      </c>
+      <c r="P425" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q425" s="2" t="inlineStr">
+        <is>
+          <t>65599</t>
+        </is>
+      </c>
+      <c r="R425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/castle-off-licence/</t>
+        </is>
+      </c>
+      <c r="S425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/castleofflicence</t>
+        </is>
+      </c>
+      <c r="T425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/castle.offy.tralee/</t>
+        </is>
+      </c>
+      <c r="U425" s="2" t="inlineStr"/>
+      <c r="V425" s="2" t="inlineStr"/>
+      <c r="W425" s="2" t="inlineStr">
+        <is>
+          <t>Fiona Palfrey</t>
+        </is>
+      </c>
+      <c r="X425" s="2" t="inlineStr">
+        <is>
+          <t>General Manager/ Director</t>
+        </is>
+      </c>
+      <c r="Y425" s="2" t="inlineStr"/>
+      <c r="Z425" s="2" t="inlineStr"/>
+      <c r="AA425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fiona-palfrey-46825722</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Woodberrys Wines</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>8060</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>Galway</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>County Galway</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>3 Middle Street Mews, Middle Street</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>H91 C2V4</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="J426" s="2" t="inlineStr"/>
+      <c r="K426" s="2" t="inlineStr"/>
+      <c r="L426" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="inlineStr"/>
+      <c r="N426" s="2" t="inlineStr">
+        <is>
+          <t>info@woodberrys.ie</t>
+        </is>
+      </c>
+      <c r="O426" s="2" t="inlineStr">
+        <is>
+          <t>+353 91 533 706</t>
+        </is>
+      </c>
+      <c r="P426" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="Q426" s="2" t="inlineStr"/>
+      <c r="R426" s="2" t="inlineStr"/>
+      <c r="S426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/woodberrys</t>
+        </is>
+      </c>
+      <c r="T426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woodberrywines/</t>
+        </is>
+      </c>
+      <c r="U426" s="2" t="inlineStr"/>
+      <c r="V426" s="2" t="inlineStr"/>
+      <c r="W426" s="2" t="inlineStr"/>
+      <c r="X426" s="2" t="inlineStr"/>
+      <c r="Y426" s="2" t="inlineStr"/>
+      <c r="Z426" s="2" t="inlineStr"/>
+      <c r="AA426" s="2" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr"/>
+      <c r="K427" s="2" t="inlineStr"/>
+      <c r="L427" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="inlineStr"/>
+      <c r="N427" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O427" s="2" t="inlineStr"/>
+      <c r="P427" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q427" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R427" s="2" t="inlineStr"/>
+      <c r="S427" s="2" t="inlineStr"/>
+      <c r="T427" s="2" t="inlineStr"/>
+      <c r="U427" s="2" t="inlineStr"/>
+      <c r="V427" s="2" t="inlineStr"/>
+      <c r="W427" s="2" t="inlineStr">
+        <is>
+          <t>John Donohoe</t>
+        </is>
+      </c>
+      <c r="X427" s="2" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="Y427" s="2" t="inlineStr"/>
+      <c r="Z427" s="2" t="inlineStr"/>
+      <c r="AA427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-donohoe-48a5a33b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>Premium Wines Limited</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>20954</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 22</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>Unit C4, Baldonnell Business Park, Nass Road</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>D22 Y242</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.premiumwineslimited.ie</t>
+        </is>
+      </c>
+      <c r="J428" s="2" t="inlineStr"/>
+      <c r="K428" s="2" t="inlineStr"/>
+      <c r="L428" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M428" s="2" t="inlineStr"/>
+      <c r="N428" s="2" t="inlineStr">
+        <is>
+          <t>premiumwineslimited@gmail.com</t>
+        </is>
+      </c>
+      <c r="O428" s="2" t="inlineStr"/>
+      <c r="P428" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q428" s="2" t="inlineStr">
+        <is>
+          <t>425358</t>
+        </is>
+      </c>
+      <c r="R428" s="2" t="inlineStr"/>
+      <c r="S428" s="2" t="inlineStr"/>
+      <c r="T428" s="2" t="inlineStr"/>
+      <c r="U428" s="2" t="inlineStr"/>
+      <c r="V428" s="2" t="inlineStr"/>
+      <c r="W428" s="2" t="inlineStr">
+        <is>
+          <t>James O’hara</t>
+        </is>
+      </c>
+      <c r="X428" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y428" s="2" t="inlineStr"/>
+      <c r="Z428" s="2" t="inlineStr"/>
+      <c r="AA428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-o-hara-45a93138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr"/>
+      <c r="K429" s="2" t="inlineStr"/>
+      <c r="L429" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M429" s="2" t="inlineStr"/>
+      <c r="N429" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O429" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P429" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q429" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U429" s="2" t="inlineStr"/>
+      <c r="V429" s="2" t="inlineStr"/>
+      <c r="W429" s="2" t="inlineStr">
+        <is>
+          <t>Marilia Carraro</t>
+        </is>
+      </c>
+      <c r="X429" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y429" s="2" t="inlineStr"/>
+      <c r="Z429" s="2" t="inlineStr"/>
+      <c r="AA429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mariliacarraro/</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr"/>
+      <c r="K430" s="2" t="inlineStr"/>
+      <c r="L430" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M430" s="2" t="inlineStr"/>
+      <c r="N430" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O430" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P430" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q430" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U430" s="2" t="inlineStr"/>
+      <c r="V430" s="2" t="inlineStr"/>
+      <c r="W430" s="2" t="inlineStr">
+        <is>
+          <t>Piero Murgia</t>
+        </is>
+      </c>
+      <c r="X430" s="2" t="inlineStr">
+        <is>
+          <t>Territory Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y430" s="2" t="inlineStr"/>
+      <c r="Z430" s="2" t="inlineStr"/>
+      <c r="AA430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/piero-murgia-313003150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>Italicatessen Ltd.</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>Newtownmountkennedy</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>County Wicklow</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>Block F, Newtown Business &amp; Enterprise Centre</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>A63 C959</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr"/>
+      <c r="K431" s="2" t="inlineStr"/>
+      <c r="L431" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M431" s="2" t="inlineStr"/>
+      <c r="N431" s="2" t="inlineStr">
+        <is>
+          <t>info@italicatessen.ie</t>
+        </is>
+      </c>
+      <c r="O431" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 201 1617</t>
+        </is>
+      </c>
+      <c r="P431" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q431" s="2" t="inlineStr">
+        <is>
+          <t>359195</t>
+        </is>
+      </c>
+      <c r="R431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italicatessen-ltd/</t>
+        </is>
+      </c>
+      <c r="S431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italicatessen/</t>
+        </is>
+      </c>
+      <c r="T431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/italicatessen_ltd/</t>
+        </is>
+      </c>
+      <c r="U431" s="2" t="inlineStr"/>
+      <c r="V431" s="2" t="inlineStr"/>
+      <c r="W431" s="2" t="inlineStr">
+        <is>
+          <t>Daragh Monahan</t>
+        </is>
+      </c>
+      <c r="X431" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Sales</t>
+        </is>
+      </c>
+      <c r="Y431" s="2" t="inlineStr"/>
+      <c r="Z431" s="2" t="inlineStr"/>
+      <c r="AA431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daragh-monahan-4716881a3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J432" s="2" t="inlineStr"/>
+      <c r="K432" s="2" t="inlineStr"/>
+      <c r="L432" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M432" s="2" t="inlineStr"/>
+      <c r="N432" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O432" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P432" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q432" s="2" t="inlineStr"/>
+      <c r="R432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U432" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V432" s="2" t="inlineStr"/>
+      <c r="W432" s="2" t="inlineStr">
+        <is>
+          <t>Avril Kirrane</t>
+        </is>
+      </c>
+      <c r="X432" s="2" t="inlineStr">
+        <is>
+          <t>Wine Specialist &amp; Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y432" s="2" t="inlineStr"/>
+      <c r="Z432" s="2" t="inlineStr"/>
+      <c r="AA432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avril-kirrane-42055115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>Boutique Wines</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>48718</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>Dublin 2</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>17 Dame Street</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>D02 FF66</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr"/>
+      <c r="K433" s="2" t="inlineStr"/>
+      <c r="L433" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M433" s="2" t="inlineStr"/>
+      <c r="N433" s="2" t="inlineStr">
+        <is>
+          <t>info@boutiquewines.ie</t>
+        </is>
+      </c>
+      <c r="O433" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 881 8811</t>
+        </is>
+      </c>
+      <c r="P433" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q433" s="2" t="inlineStr"/>
+      <c r="R433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/boutique-wines-ltd/</t>
+        </is>
+      </c>
+      <c r="S433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutiquewines/</t>
+        </is>
+      </c>
+      <c r="T433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutiquewines</t>
+        </is>
+      </c>
+      <c r="U433" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BoutiqueWinesie</t>
+        </is>
+      </c>
+      <c r="V433" s="2" t="inlineStr"/>
+      <c r="W433" s="2" t="inlineStr">
+        <is>
+          <t>Johnny Mcmorrough</t>
+        </is>
+      </c>
+      <c r="X433" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y433" s="2" t="inlineStr"/>
+      <c r="Z433" s="2" t="inlineStr"/>
+      <c r="AA433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johnny-mcmorrough-32597a3a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>Le Caveau Ltd.</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>Kilkenny</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Co. Kilkenny</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>Market Yard</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>R95 FH05</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>https://lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr"/>
+      <c r="K434" s="2" t="inlineStr"/>
+      <c r="L434" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="inlineStr"/>
+      <c r="N434" s="2" t="inlineStr">
+        <is>
+          <t>orders@lecaveau.ie</t>
+        </is>
+      </c>
+      <c r="O434" s="2" t="inlineStr">
+        <is>
+          <t>+353 56 775 2166</t>
+        </is>
+      </c>
+      <c r="P434" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q434" s="2" t="inlineStr">
+        <is>
+          <t>311736</t>
+        </is>
+      </c>
+      <c r="R434" s="2" t="inlineStr"/>
+      <c r="S434" s="2" t="inlineStr"/>
+      <c r="T434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lecaveauwinemerchants</t>
+        </is>
+      </c>
+      <c r="U434" s="2" t="inlineStr"/>
+      <c r="V434" s="2" t="inlineStr"/>
+      <c r="W434" s="2" t="inlineStr">
+        <is>
+          <t>Pascal Rossignol</t>
+        </is>
+      </c>
+      <c r="X434" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Owner</t>
+        </is>
+      </c>
+      <c r="Y434" s="2" t="inlineStr"/>
+      <c r="Z434" s="2" t="inlineStr"/>
+      <c r="AA434" s="2" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>Macguinness Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>23827</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>Co. Louth</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>Williamson's Mall, Francis Street, Townparks</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>A91 NR29</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr"/>
+      <c r="K435" s="2" t="inlineStr"/>
+      <c r="L435" s="2" t="inlineStr"/>
+      <c r="M435" s="2" t="inlineStr"/>
+      <c r="N435" s="2" t="inlineStr">
+        <is>
+          <t>info@dundalkwines.com</t>
+        </is>
+      </c>
+      <c r="O435" s="2" t="inlineStr"/>
+      <c r="P435" s="2" t="inlineStr"/>
+      <c r="Q435" s="2" t="inlineStr"/>
+      <c r="R435" s="2" t="inlineStr"/>
+      <c r="S435" s="2" t="inlineStr"/>
+      <c r="T435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/macguinnesswine/</t>
+        </is>
+      </c>
+      <c r="U435" s="2" t="inlineStr"/>
+      <c r="V435" s="2" t="inlineStr"/>
+      <c r="W435" s="2" t="inlineStr">
+        <is>
+          <t>Alan Mac Guinness Rockwines</t>
+        </is>
+      </c>
+      <c r="X435" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y435" s="2" t="inlineStr"/>
+      <c r="Z435" s="2" t="inlineStr"/>
+      <c r="AA435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alan-mac-guinness-rockwines-69839624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>P. Sweeney Ventures Limited</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>42229</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>County Dublin</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>117 Philipsburgh Avenue, Fairview</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>D03 XV04</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>https://sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="J436" s="2" t="inlineStr"/>
+      <c r="K436" s="2" t="inlineStr"/>
+      <c r="L436" s="2" t="inlineStr"/>
+      <c r="M436" s="2" t="inlineStr"/>
+      <c r="N436" s="2" t="inlineStr">
+        <is>
+          <t>info@sweeneysd3.ie</t>
+        </is>
+      </c>
+      <c r="O436" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 837 2857</t>
+        </is>
+      </c>
+      <c r="P436" s="2" t="inlineStr"/>
+      <c r="Q436" s="2" t="inlineStr"/>
+      <c r="R436" s="2" t="inlineStr"/>
+      <c r="S436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Sweeneysd3/</t>
+        </is>
+      </c>
+      <c r="T436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="U436" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/sweeneysd3</t>
+        </is>
+      </c>
+      <c r="V436" s="2" t="inlineStr"/>
+      <c r="W436" s="2" t="inlineStr"/>
+      <c r="X436" s="2" t="inlineStr"/>
+      <c r="Y436" s="2" t="inlineStr"/>
+      <c r="Z436" s="2" t="inlineStr"/>
+      <c r="AA436" s="2" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>O'brien Retail Concepts Limited</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>46310</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>Carry Out Tyrellstown, Unit 7 The Plaza, Tyrellstown Town Centre, Tyrrelstown</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>D15 XF21</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecru.ie</t>
+        </is>
+      </c>
+      <c r="J437" s="2" t="inlineStr"/>
+      <c r="K437" s="2" t="inlineStr"/>
+      <c r="L437" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M437" s="2" t="inlineStr"/>
+      <c r="N437" s="2" t="inlineStr">
+        <is>
+          <t>Orders@TheCru.ie</t>
+        </is>
+      </c>
+      <c r="O437" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 485 3171</t>
+        </is>
+      </c>
+      <c r="P437" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q437" s="2" t="inlineStr"/>
+      <c r="R437" s="2" t="inlineStr"/>
+      <c r="S437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com//thecru.ie</t>
+        </is>
+      </c>
+      <c r="T437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thecru.ie</t>
+        </is>
+      </c>
+      <c r="U437" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/TheCru_IE</t>
+        </is>
+      </c>
+      <c r="V437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCNRk_PWRb3yOQK77FxGVe6g/featured</t>
+        </is>
+      </c>
+      <c r="W437" s="2" t="inlineStr"/>
+      <c r="X437" s="2" t="inlineStr"/>
+      <c r="Y437" s="2" t="inlineStr"/>
+      <c r="Z437" s="2" t="inlineStr"/>
+      <c r="AA437" s="2" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>James Redmond &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>21158</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>25 Ranelagh, Ranelagh</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>D06 RP40</t>
+        </is>
+      </c>
+      <c r="I438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.redmonds.ie</t>
+        </is>
+      </c>
+      <c r="J438" s="2" t="inlineStr"/>
+      <c r="K438" s="2" t="inlineStr"/>
+      <c r="L438" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M438" s="2" t="inlineStr"/>
+      <c r="N438" s="2" t="inlineStr">
+        <is>
+          <t>info@redmonds.ie</t>
+        </is>
+      </c>
+      <c r="O438" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 496 0552</t>
+        </is>
+      </c>
+      <c r="P438" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q438" s="2" t="inlineStr">
+        <is>
+          <t>51847</t>
+        </is>
+      </c>
+      <c r="R438" s="2" t="inlineStr"/>
+      <c r="S438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/redmonds-off-licence-ranelagh-120637134043/</t>
+        </is>
+      </c>
+      <c r="T438" s="2" t="inlineStr">
+        <is>
+          <t>http://instagram.com/redmondsd6</t>
+        </is>
+      </c>
+      <c r="U438" s="2" t="inlineStr"/>
+      <c r="V438" s="2" t="inlineStr"/>
+      <c r="W438" s="2" t="inlineStr"/>
+      <c r="X438" s="2" t="inlineStr"/>
+      <c r="Y438" s="2" t="inlineStr"/>
+      <c r="Z438" s="2" t="inlineStr"/>
+      <c r="AA438" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
